--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -10876,16 +10876,8 @@
       <c r="K14" s="519" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>EDIFICIO DE APARTAMENTOS 12 PISOS - BOGOTÁ D.C.</t>
-        </is>
-      </c>
+      <c r="A15" s="60" t="n"/>
+      <c r="B15" s="35" t="n"/>
       <c r="C15" s="36" t="n"/>
       <c r="D15" s="1281" t="n"/>
       <c r="E15" s="1281" t="n"/>
@@ -10895,16 +10887,8 @@
       <c r="K15" s="519" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="1051">
-      <c r="A16" s="156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="157" t="inlineStr">
-        <is>
-          <t>FASE 1 - PRELIMINARES, ESTUDIOS Y DISEÑOS</t>
-        </is>
-      </c>
+      <c r="A16" s="156" t="n"/>
+      <c r="B16" s="157" t="n"/>
       <c r="C16" s="158" t="n"/>
       <c r="D16" s="1282" t="n"/>
       <c r="E16" s="1282" t="n"/>
@@ -10916,16 +10900,8 @@
       <c r="K16" s="703" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="153" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="B17" s="154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Estudios y diseños</t>
-        </is>
-      </c>
+      <c r="A17" s="153" t="n"/>
+      <c r="B17" s="154" t="n"/>
       <c r="C17" s="155" t="n"/>
       <c r="D17" s="1283" t="n"/>
       <c r="E17" s="1283" t="n"/>
@@ -10934,16 +10910,8 @@
       <c r="H17" s="693" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="63" t="inlineStr">
-        <is>
-          <t>1.1.1</t>
-        </is>
-      </c>
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
+      <c r="A18" s="63" t="n"/>
+      <c r="B18" s="41" t="n"/>
       <c r="C18" s="128" t="n"/>
       <c r="D18" s="1284" t="n"/>
       <c r="E18" s="1284" t="n"/>
@@ -10952,16 +10920,8 @@
       <c r="H18" s="691" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="63" t="inlineStr">
-        <is>
-          <t>1.1.2</t>
-        </is>
-      </c>
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Diseño arquitectónico y estructural</t>
-        </is>
-      </c>
+      <c r="A19" s="63" t="n"/>
+      <c r="B19" s="41" t="n"/>
       <c r="C19" s="128" t="n"/>
       <c r="D19" s="1284" t="n"/>
       <c r="E19" s="1284" t="n"/>
@@ -10970,16 +10930,8 @@
       <c r="H19" s="691" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="64" t="inlineStr">
-        <is>
-          <t>1.1.3</t>
-        </is>
-      </c>
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Diseño hidrosanitario, eléctrico y de gas</t>
-        </is>
-      </c>
+      <c r="A20" s="64" t="n"/>
+      <c r="B20" s="42" t="n"/>
       <c r="C20" s="129" t="n"/>
       <c r="D20" s="1285" t="n"/>
       <c r="E20" s="1285" t="n"/>
@@ -10988,16 +10940,8 @@
       <c r="H20" s="686" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="63" t="inlineStr">
-        <is>
-          <t>1.1.4</t>
-        </is>
-      </c>
-      <c r="B21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Trámite y expedición de licencia de construcción (curaduría)</t>
-        </is>
-      </c>
+      <c r="A21" s="63" t="n"/>
+      <c r="B21" s="41" t="n"/>
       <c r="C21" s="128" t="n"/>
       <c r="D21" s="1284" t="n"/>
       <c r="E21" s="1284" t="n"/>
@@ -11006,16 +10950,8 @@
       <c r="H21" s="691" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Preliminares en el predio</t>
-        </is>
-      </c>
+      <c r="A22" s="62" t="n"/>
+      <c r="B22" s="39" t="n"/>
       <c r="C22" s="40" t="n"/>
       <c r="D22" s="1286" t="n"/>
       <c r="E22" s="1286" t="n"/>
@@ -11024,16 +10960,8 @@
       <c r="H22" s="693" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="63" t="inlineStr">
-        <is>
-          <t>1.2.1</t>
-        </is>
-      </c>
-      <c r="B23" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cerramiento provisional, campamento y oficina de obra</t>
-        </is>
-      </c>
+      <c r="A23" s="63" t="n"/>
+      <c r="B23" s="41" t="n"/>
       <c r="C23" s="128" t="n"/>
       <c r="D23" s="1284" t="n"/>
       <c r="E23" s="1284" t="n"/>
@@ -11042,16 +10970,8 @@
       <c r="H23" s="691" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="64" t="inlineStr">
-        <is>
-          <t>1.2.2</t>
-        </is>
-      </c>
-      <c r="B24" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Localización y replanteo topográfico general</t>
-        </is>
-      </c>
+      <c r="A24" s="64" t="n"/>
+      <c r="B24" s="42" t="n"/>
       <c r="C24" s="129" t="n"/>
       <c r="D24" s="1285" t="n"/>
       <c r="E24" s="1285" t="n"/>
@@ -11060,16 +10980,8 @@
       <c r="H24" s="686" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="63" t="inlineStr">
-        <is>
-          <t>1.2.3</t>
-        </is>
-      </c>
-      <c r="B25" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Descapote, demolición de estructuras existentes y limpieza</t>
-        </is>
-      </c>
+      <c r="A25" s="63" t="n"/>
+      <c r="B25" s="41" t="n"/>
       <c r="C25" s="128" t="n"/>
       <c r="D25" s="1284" t="n"/>
       <c r="E25" s="1284" t="n"/>
@@ -11078,16 +10990,8 @@
       <c r="H25" s="691" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="63" t="inlineStr">
-        <is>
-          <t>1.2.4</t>
-        </is>
-      </c>
-      <c r="B26" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Inicio de obra civil (fin de preliminares)</t>
-        </is>
-      </c>
+      <c r="A26" s="63" t="n"/>
+      <c r="B26" s="41" t="n"/>
       <c r="C26" s="128" t="n"/>
       <c r="D26" s="1284" t="n"/>
       <c r="E26" s="1284" t="n"/>
@@ -11096,16 +11000,8 @@
       <c r="H26" s="691" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="1051">
-      <c r="A27" s="61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B27" s="37" t="inlineStr">
-        <is>
-          <t>FASE 2 - EXCAVACIÓN Y CIMENTACIÓN</t>
-        </is>
-      </c>
+      <c r="A27" s="61" t="n"/>
+      <c r="B27" s="37" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="1287" t="n"/>
       <c r="E27" s="1287" t="n"/>
@@ -11114,16 +11010,8 @@
       <c r="H27" s="561" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B28" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Excavación y contención</t>
-        </is>
-      </c>
+      <c r="A28" s="62" t="n"/>
+      <c r="B28" s="39" t="n"/>
       <c r="C28" s="40" t="n"/>
       <c r="D28" s="1286" t="n"/>
       <c r="E28" s="1286" t="n"/>
@@ -11132,16 +11020,8 @@
       <c r="H28" s="693" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="63" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="B29" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Excavación mecánica de sótanos (2 niveles)</t>
-        </is>
-      </c>
+      <c r="A29" s="63" t="n"/>
+      <c r="B29" s="41" t="n"/>
       <c r="C29" s="128" t="n"/>
       <c r="D29" s="1284" t="n"/>
       <c r="E29" s="1284" t="n"/>
@@ -11150,16 +11030,8 @@
       <c r="H29" s="691" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="64" t="inlineStr">
-        <is>
-          <t>2.1.2</t>
-        </is>
-      </c>
-      <c r="B30" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cargue, transporte y disposición final de material sobrante</t>
-        </is>
-      </c>
+      <c r="A30" s="64" t="n"/>
+      <c r="B30" s="42" t="n"/>
       <c r="C30" s="129" t="n"/>
       <c r="D30" s="1285" t="n"/>
       <c r="E30" s="1285" t="n"/>
@@ -11168,16 +11040,8 @@
       <c r="H30" s="686" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="63" t="inlineStr">
-        <is>
-          <t>2.1.3</t>
-        </is>
-      </c>
-      <c r="B31" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Entibado y contención perimetral (pantalla anclada)</t>
-        </is>
-      </c>
+      <c r="A31" s="63" t="n"/>
+      <c r="B31" s="41" t="n"/>
       <c r="C31" s="128" t="n"/>
       <c r="D31" s="1284" t="n"/>
       <c r="E31" s="1284" t="n"/>
@@ -11186,16 +11050,8 @@
       <c r="H31" s="691" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B32" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Cimentación en concreto</t>
-        </is>
-      </c>
+      <c r="A32" s="62" t="n"/>
+      <c r="B32" s="39" t="n"/>
       <c r="C32" s="40" t="n"/>
       <c r="D32" s="1286" t="n"/>
       <c r="E32" s="1286" t="n"/>
@@ -11204,16 +11060,8 @@
       <c r="H32" s="693" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="inlineStr">
-        <is>
-          <t>2.2.1</t>
-        </is>
-      </c>
-      <c r="B33" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Solado o cimiento ciclópeo de limpieza</t>
-        </is>
-      </c>
+      <c r="A33" s="63" t="n"/>
+      <c r="B33" s="41" t="n"/>
       <c r="C33" s="128" t="n"/>
       <c r="D33" s="1284" t="n"/>
       <c r="E33" s="1284" t="n"/>
@@ -11222,16 +11070,8 @@
       <c r="H33" s="691" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="63" t="inlineStr">
-        <is>
-          <t>2.2.2</t>
-        </is>
-      </c>
-      <c r="B34" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Armado de acero de refuerzo - zapatas, dados y arranques de columna</t>
-        </is>
-      </c>
+      <c r="A34" s="63" t="n"/>
+      <c r="B34" s="41" t="n"/>
       <c r="C34" s="128" t="n"/>
       <c r="D34" s="1284" t="n"/>
       <c r="E34" s="1284" t="n"/>
@@ -11240,16 +11080,8 @@
       <c r="H34" s="691" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="63" t="inlineStr">
-        <is>
-          <t>2.2.3</t>
-        </is>
-      </c>
-      <c r="B35" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Fundida de zapatas y dados en concreto 3000 PSI</t>
-        </is>
-      </c>
+      <c r="A35" s="63" t="n"/>
+      <c r="B35" s="41" t="n"/>
       <c r="C35" s="128" t="n"/>
       <c r="D35" s="1284" t="n"/>
       <c r="E35" s="1284" t="n"/>
@@ -11258,16 +11090,8 @@
       <c r="H35" s="691" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="63" t="inlineStr">
-        <is>
-          <t>2.2.4</t>
-        </is>
-      </c>
-      <c r="B36" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Armado de acero de refuerzo - muros de contención</t>
-        </is>
-      </c>
+      <c r="A36" s="63" t="n"/>
+      <c r="B36" s="41" t="n"/>
       <c r="C36" s="128" t="n"/>
       <c r="D36" s="1284" t="n"/>
       <c r="E36" s="1284" t="n"/>
@@ -11276,16 +11100,8 @@
       <c r="H36" s="691" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="63" t="inlineStr">
-        <is>
-          <t>2.2.5</t>
-        </is>
-      </c>
-      <c r="B37" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Formaleta y fundida de muros de contención en concreto reforzado 3000 PSI</t>
-        </is>
-      </c>
+      <c r="A37" s="63" t="n"/>
+      <c r="B37" s="41" t="n"/>
       <c r="C37" s="128" t="n"/>
       <c r="D37" s="1284" t="n"/>
       <c r="E37" s="1284" t="n"/>
@@ -11294,16 +11110,8 @@
       <c r="H37" s="691" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="64" t="inlineStr">
-        <is>
-          <t>2.2.6</t>
-        </is>
-      </c>
-      <c r="B38" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Vigas de cimentación (armado y fundida)</t>
-        </is>
-      </c>
+      <c r="A38" s="64" t="n"/>
+      <c r="B38" s="42" t="n"/>
       <c r="C38" s="129" t="n"/>
       <c r="D38" s="1285" t="n"/>
       <c r="E38" s="1285" t="n"/>
@@ -11312,16 +11120,8 @@
       <c r="H38" s="686" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="65" t="inlineStr">
-        <is>
-          <t>2.2.7</t>
-        </is>
-      </c>
-      <c r="B39" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Losa de cimentación / placa contrapiso sótano e=0.15m</t>
-        </is>
-      </c>
+      <c r="A39" s="65" t="n"/>
+      <c r="B39" s="43" t="n"/>
       <c r="C39" s="130" t="n"/>
       <c r="D39" s="1288" t="n"/>
       <c r="E39" s="1288" t="n"/>
@@ -11330,16 +11130,8 @@
       <c r="H39" s="684" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="63" t="inlineStr">
-        <is>
-          <t>2.2.8</t>
-        </is>
-      </c>
-      <c r="B40" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Impermeabilización de cimentación y muros de contención</t>
-        </is>
-      </c>
+      <c r="A40" s="63" t="n"/>
+      <c r="B40" s="41" t="n"/>
       <c r="C40" s="128" t="n"/>
       <c r="D40" s="1284" t="n"/>
       <c r="E40" s="1284" t="n"/>
@@ -11348,16 +11140,8 @@
       <c r="H40" s="691" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="63" t="inlineStr">
-        <is>
-          <t>2.2.9</t>
-        </is>
-      </c>
-      <c r="B41" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Cimentación terminada</t>
-        </is>
-      </c>
+      <c r="A41" s="63" t="n"/>
+      <c r="B41" s="41" t="n"/>
       <c r="C41" s="128" t="n"/>
       <c r="D41" s="1284" t="n"/>
       <c r="E41" s="1284" t="n"/>
@@ -11366,16 +11150,8 @@
       <c r="H41" s="691" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="1051">
-      <c r="A42" s="66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B42" s="667" t="inlineStr">
-        <is>
-          <t>FASE 3 - ESTRUCTURA EN CONCRETO (SUPERESTRUCTURA)</t>
-        </is>
-      </c>
+      <c r="A42" s="66" t="n"/>
+      <c r="B42" s="667" t="n"/>
       <c r="C42" s="44" t="n"/>
       <c r="D42" s="1289" t="n"/>
       <c r="E42" s="1289" t="n"/>
@@ -11384,16 +11160,8 @@
       <c r="H42" s="717" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Estructura de sótanos</t>
-        </is>
-      </c>
+      <c r="A43" s="62" t="n"/>
+      <c r="B43" s="39" t="n"/>
       <c r="C43" s="40" t="n"/>
       <c r="D43" s="1286" t="n"/>
       <c r="E43" s="1286" t="n"/>
@@ -11402,16 +11170,8 @@
       <c r="H43" s="693" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="63" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="B44" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura sótano 1 (columnas, vigas, placa)</t>
-        </is>
-      </c>
+      <c r="A44" s="63" t="n"/>
+      <c r="B44" s="41" t="n"/>
       <c r="C44" s="128" t="n"/>
       <c r="D44" s="1284" t="n"/>
       <c r="E44" s="1284" t="n"/>
@@ -11420,16 +11180,8 @@
       <c r="H44" s="691" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="63" t="inlineStr">
-        <is>
-          <t>3.1.2</t>
-        </is>
-      </c>
-      <c r="B45" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura sótano 2 (columnas, vigas, placa)</t>
-        </is>
-      </c>
+      <c r="A45" s="63" t="n"/>
+      <c r="B45" s="41" t="n"/>
       <c r="C45" s="128" t="n"/>
       <c r="D45" s="1284" t="n"/>
       <c r="E45" s="1284" t="n"/>
@@ -11438,16 +11190,8 @@
       <c r="H45" s="691" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="62" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Estructura de la torre (pisos 1 a 12)</t>
-        </is>
-      </c>
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="39" t="n"/>
       <c r="C46" s="40" t="n"/>
       <c r="D46" s="1286" t="n"/>
       <c r="E46" s="1286" t="n"/>
@@ -11456,16 +11200,8 @@
       <c r="H46" s="693" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="63" t="inlineStr">
-        <is>
-          <t>3.2.1</t>
-        </is>
-      </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 1 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A47" s="63" t="n"/>
+      <c r="B47" s="41" t="n"/>
       <c r="C47" s="128" t="n"/>
       <c r="D47" s="1284" t="n"/>
       <c r="E47" s="1284" t="n"/>
@@ -11474,16 +11210,8 @@
       <c r="H47" s="691" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="63" t="inlineStr">
-        <is>
-          <t>3.2.2</t>
-        </is>
-      </c>
-      <c r="B48" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 2 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A48" s="63" t="n"/>
+      <c r="B48" s="41" t="n"/>
       <c r="C48" s="128" t="n"/>
       <c r="D48" s="1284" t="n"/>
       <c r="E48" s="1284" t="n"/>
@@ -11492,16 +11220,8 @@
       <c r="H48" s="691" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="63" t="inlineStr">
-        <is>
-          <t>3.2.3</t>
-        </is>
-      </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 3 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A49" s="63" t="n"/>
+      <c r="B49" s="41" t="n"/>
       <c r="C49" s="128" t="n"/>
       <c r="D49" s="1284" t="n"/>
       <c r="E49" s="1284" t="n"/>
@@ -11510,16 +11230,8 @@
       <c r="H49" s="691" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="63" t="inlineStr">
-        <is>
-          <t>3.2.4</t>
-        </is>
-      </c>
-      <c r="B50" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 4 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A50" s="63" t="n"/>
+      <c r="B50" s="41" t="n"/>
       <c r="C50" s="128" t="n"/>
       <c r="D50" s="1284" t="n"/>
       <c r="E50" s="1284" t="n"/>
@@ -11528,16 +11240,8 @@
       <c r="H50" s="691" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="63" t="inlineStr">
-        <is>
-          <t>3.2.5</t>
-        </is>
-      </c>
-      <c r="B51" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 5 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A51" s="63" t="n"/>
+      <c r="B51" s="41" t="n"/>
       <c r="C51" s="128" t="n"/>
       <c r="D51" s="1284" t="n"/>
       <c r="E51" s="1284" t="n"/>
@@ -11546,16 +11250,8 @@
       <c r="H51" s="691" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="64" t="inlineStr">
-        <is>
-          <t>3.2.6</t>
-        </is>
-      </c>
-      <c r="B52" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 6 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A52" s="64" t="n"/>
+      <c r="B52" s="42" t="n"/>
       <c r="C52" s="129" t="n"/>
       <c r="D52" s="1285" t="n"/>
       <c r="E52" s="1285" t="n"/>
@@ -11564,16 +11260,8 @@
       <c r="H52" s="686" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="65" t="inlineStr">
-        <is>
-          <t>3.2.7</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 7 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A53" s="65" t="n"/>
+      <c r="B53" s="43" t="n"/>
       <c r="C53" s="130" t="n"/>
       <c r="D53" s="1288" t="n"/>
       <c r="E53" s="1288" t="n"/>
@@ -11582,16 +11270,8 @@
       <c r="H53" s="684" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="64" t="inlineStr">
-        <is>
-          <t>3.2.8</t>
-        </is>
-      </c>
-      <c r="B54" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 8 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A54" s="64" t="n"/>
+      <c r="B54" s="42" t="n"/>
       <c r="C54" s="129" t="n"/>
       <c r="D54" s="1285" t="n"/>
       <c r="E54" s="1285" t="n"/>
@@ -11600,16 +11280,8 @@
       <c r="H54" s="686" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="65" t="inlineStr">
-        <is>
-          <t>3.2.9</t>
-        </is>
-      </c>
-      <c r="B55" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 9 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A55" s="65" t="n"/>
+      <c r="B55" s="43" t="n"/>
       <c r="C55" s="130" t="n"/>
       <c r="D55" s="1288" t="n"/>
       <c r="E55" s="1288" t="n"/>
@@ -11618,16 +11290,8 @@
       <c r="H55" s="684" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="64" t="inlineStr">
-        <is>
-          <t>3.2.10</t>
-        </is>
-      </c>
-      <c r="B56" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 10 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A56" s="64" t="n"/>
+      <c r="B56" s="42" t="n"/>
       <c r="C56" s="129" t="n"/>
       <c r="D56" s="1285" t="n"/>
       <c r="E56" s="1285" t="n"/>
@@ -11636,16 +11300,8 @@
       <c r="H56" s="686" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="65" t="inlineStr">
-        <is>
-          <t>3.2.11</t>
-        </is>
-      </c>
-      <c r="B57" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 11 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A57" s="65" t="n"/>
+      <c r="B57" s="43" t="n"/>
       <c r="C57" s="130" t="n"/>
       <c r="D57" s="1288" t="n"/>
       <c r="E57" s="1288" t="n"/>
@@ -11654,16 +11310,8 @@
       <c r="H57" s="684" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="64" t="inlineStr">
-        <is>
-          <t>3.2.12</t>
-        </is>
-      </c>
-      <c r="B58" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estructura piso 12 (columnas, vigas, placa de entrepiso)</t>
-        </is>
-      </c>
+      <c r="A58" s="64" t="n"/>
+      <c r="B58" s="42" t="n"/>
       <c r="C58" s="129" t="n"/>
       <c r="D58" s="1285" t="n"/>
       <c r="E58" s="1285" t="n"/>
@@ -11672,16 +11320,8 @@
       <c r="H58" s="686" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="62" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B59" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Cubierta y remates estructurales</t>
-        </is>
-      </c>
+      <c r="A59" s="62" t="n"/>
+      <c r="B59" s="39" t="n"/>
       <c r="C59" s="40" t="n"/>
       <c r="D59" s="1286" t="n"/>
       <c r="E59" s="1286" t="n"/>
@@ -11690,16 +11330,8 @@
       <c r="H59" s="693" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="64" t="inlineStr">
-        <is>
-          <t>3.3.1</t>
-        </is>
-      </c>
-      <c r="B60" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Placa de cubierta y cuarto de máquinas</t>
-        </is>
-      </c>
+      <c r="A60" s="64" t="n"/>
+      <c r="B60" s="42" t="n"/>
       <c r="C60" s="129" t="n"/>
       <c r="D60" s="1285" t="n"/>
       <c r="E60" s="1285" t="n"/>
@@ -11708,16 +11340,8 @@
       <c r="H60" s="686" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="65" t="inlineStr">
-        <is>
-          <t>3.3.2</t>
-        </is>
-      </c>
-      <c r="B61" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Losa de tanque elevado</t>
-        </is>
-      </c>
+      <c r="A61" s="65" t="n"/>
+      <c r="B61" s="43" t="n"/>
       <c r="C61" s="130" t="n"/>
       <c r="D61" s="1288" t="n"/>
       <c r="E61" s="1288" t="n"/>
@@ -11726,16 +11350,8 @@
       <c r="H61" s="684" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="64" t="inlineStr">
-        <is>
-          <t>3.3.3</t>
-        </is>
-      </c>
-      <c r="B62" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Estructura de la torre terminada (topo de obra gris)</t>
-        </is>
-      </c>
+      <c r="A62" s="64" t="n"/>
+      <c r="B62" s="42" t="n"/>
       <c r="C62" s="129" t="n"/>
       <c r="D62" s="1285" t="n"/>
       <c r="E62" s="1285" t="n"/>
@@ -11744,16 +11360,8 @@
       <c r="H62" s="686" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="1051">
-      <c r="A63" s="61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B63" s="37" t="inlineStr">
-        <is>
-          <t>FASE 4 - MAMPOSTERÍA Y PAÑETES</t>
-        </is>
-      </c>
+      <c r="A63" s="61" t="n"/>
+      <c r="B63" s="37" t="n"/>
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="1290" t="n"/>
       <c r="E63" s="1290" t="n"/>
@@ -11762,16 +11370,8 @@
       <c r="H63" s="692" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="64" t="inlineStr">
-        <is>
-          <t>4.0.1</t>
-        </is>
-      </c>
-      <c r="B64" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Mampostería y pañetes - sótanos</t>
-        </is>
-      </c>
+      <c r="A64" s="64" t="n"/>
+      <c r="B64" s="42" t="n"/>
       <c r="C64" s="129" t="n"/>
       <c r="D64" s="1285" t="n"/>
       <c r="E64" s="1285" t="n"/>
@@ -11780,16 +11380,8 @@
       <c r="H64" s="686" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="63" t="inlineStr">
-        <is>
-          <t>4.0.2</t>
-        </is>
-      </c>
-      <c r="B65" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Mampostería y pañetes - pisos 1 a 4</t>
-        </is>
-      </c>
+      <c r="A65" s="63" t="n"/>
+      <c r="B65" s="41" t="n"/>
       <c r="C65" s="128" t="n"/>
       <c r="D65" s="1284" t="n"/>
       <c r="E65" s="1284" t="n"/>
@@ -11798,16 +11390,8 @@
       <c r="H65" s="691" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="63" t="inlineStr">
-        <is>
-          <t>4.0.3</t>
-        </is>
-      </c>
-      <c r="B66" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Mampostería y pañetes - pisos 5 a 8</t>
-        </is>
-      </c>
+      <c r="A66" s="63" t="n"/>
+      <c r="B66" s="41" t="n"/>
       <c r="C66" s="128" t="n"/>
       <c r="D66" s="1284" t="n"/>
       <c r="E66" s="1284" t="n"/>
@@ -11816,16 +11400,8 @@
       <c r="H66" s="691" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="63" t="inlineStr">
-        <is>
-          <t>4.0.4</t>
-        </is>
-      </c>
-      <c r="B67" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Mampostería y pañetes - pisos 9 a 12</t>
-        </is>
-      </c>
+      <c r="A67" s="63" t="n"/>
+      <c r="B67" s="41" t="n"/>
       <c r="C67" s="128" t="n"/>
       <c r="D67" s="1284" t="n"/>
       <c r="E67" s="1284" t="n"/>
@@ -11834,16 +11410,8 @@
       <c r="H67" s="691" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="63" t="inlineStr">
-        <is>
-          <t>4.0.5</t>
-        </is>
-      </c>
-      <c r="B68" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Mampostería y pañetes terminados</t>
-        </is>
-      </c>
+      <c r="A68" s="63" t="n"/>
+      <c r="B68" s="41" t="n"/>
       <c r="C68" s="128" t="n"/>
       <c r="D68" s="1284" t="n"/>
       <c r="E68" s="1284" t="n"/>
@@ -11852,16 +11420,8 @@
       <c r="H68" s="691" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="1051">
-      <c r="A69" s="61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B69" s="37" t="inlineStr">
-        <is>
-          <t>FASE 5 - CUBIERTA E IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
+      <c r="A69" s="61" t="n"/>
+      <c r="B69" s="37" t="n"/>
       <c r="C69" s="131" t="n"/>
       <c r="D69" s="1290" t="n"/>
       <c r="E69" s="1290" t="n"/>
@@ -11870,16 +11430,8 @@
       <c r="H69" s="692" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="64" t="inlineStr">
-        <is>
-          <t>5.0.1</t>
-        </is>
-      </c>
-      <c r="B70" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cubierta en teja termoacústica sobre estructura metálica</t>
-        </is>
-      </c>
+      <c r="A70" s="64" t="n"/>
+      <c r="B70" s="42" t="n"/>
       <c r="C70" s="129" t="n"/>
       <c r="D70" s="1285" t="n"/>
       <c r="E70" s="1285" t="n"/>
@@ -11888,16 +11440,8 @@
       <c r="H70" s="686" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="65" t="inlineStr">
-        <is>
-          <t>5.0.2</t>
-        </is>
-      </c>
-      <c r="B71" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Impermeabilización de cubiertas, terrazas y balcones</t>
-        </is>
-      </c>
+      <c r="A71" s="65" t="n"/>
+      <c r="B71" s="43" t="n"/>
       <c r="C71" s="130" t="n"/>
       <c r="D71" s="1288" t="n"/>
       <c r="E71" s="1288" t="n"/>
@@ -11906,16 +11450,8 @@
       <c r="H71" s="684" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="64" t="inlineStr">
-        <is>
-          <t>5.0.3</t>
-        </is>
-      </c>
-      <c r="B72" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Canales, bajantes de aguas lluvias y cuarto de máquinas/tanques</t>
-        </is>
-      </c>
+      <c r="A72" s="64" t="n"/>
+      <c r="B72" s="42" t="n"/>
       <c r="C72" s="129" t="n"/>
       <c r="D72" s="1285" t="n"/>
       <c r="E72" s="1285" t="n"/>
@@ -11924,16 +11460,8 @@
       <c r="H72" s="686" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="65" t="inlineStr">
-        <is>
-          <t>5.0.4</t>
-        </is>
-      </c>
-      <c r="B73" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Edificio bajo cubierta (dry-in)</t>
-        </is>
-      </c>
+      <c r="A73" s="65" t="n"/>
+      <c r="B73" s="43" t="n"/>
       <c r="C73" s="130" t="n"/>
       <c r="D73" s="1288" t="n"/>
       <c r="E73" s="1288" t="n"/>
@@ -11942,16 +11470,8 @@
       <c r="H73" s="684" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="1051">
-      <c r="A74" s="61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B74" s="37" t="inlineStr">
-        <is>
-          <t>FASE 6 - INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
+      <c r="A74" s="61" t="n"/>
+      <c r="B74" s="37" t="n"/>
       <c r="C74" s="131" t="n"/>
       <c r="D74" s="1290" t="n"/>
       <c r="E74" s="1290" t="n"/>
@@ -11960,16 +11480,8 @@
       <c r="H74" s="692" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="65" t="inlineStr">
-        <is>
-          <t>6.0.1</t>
-        </is>
-      </c>
-      <c r="B75" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Redes hidrosanitarias (punto agua/desagüe) - pisos 1 a 4</t>
-        </is>
-      </c>
+      <c r="A75" s="65" t="n"/>
+      <c r="B75" s="43" t="n"/>
       <c r="C75" s="130" t="n"/>
       <c r="D75" s="1288" t="n"/>
       <c r="E75" s="1288" t="n"/>
@@ -11978,16 +11490,8 @@
       <c r="H75" s="684" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="64" t="inlineStr">
-        <is>
-          <t>6.0.2</t>
-        </is>
-      </c>
-      <c r="B76" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Redes hidrosanitarias (punto agua/desagüe) - pisos 5 a 8</t>
-        </is>
-      </c>
+      <c r="A76" s="64" t="n"/>
+      <c r="B76" s="42" t="n"/>
       <c r="C76" s="129" t="n"/>
       <c r="D76" s="1285" t="n"/>
       <c r="E76" s="1285" t="n"/>
@@ -11996,16 +11500,8 @@
       <c r="H76" s="686" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="65" t="inlineStr">
-        <is>
-          <t>6.0.3</t>
-        </is>
-      </c>
-      <c r="B77" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Redes hidrosanitarias (punto agua/desagüe) - pisos 9 a 12</t>
-        </is>
-      </c>
+      <c r="A77" s="65" t="n"/>
+      <c r="B77" s="43" t="n"/>
       <c r="C77" s="130" t="n"/>
       <c r="D77" s="1288" t="n"/>
       <c r="E77" s="1288" t="n"/>
@@ -12014,16 +11510,8 @@
       <c r="H77" s="684" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="64" t="inlineStr">
-        <is>
-          <t>6.0.4</t>
-        </is>
-      </c>
-      <c r="B78" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cuarto de bombas, tanques de reserva y sistema hidroneumático</t>
-        </is>
-      </c>
+      <c r="A78" s="64" t="n"/>
+      <c r="B78" s="42" t="n"/>
       <c r="C78" s="129" t="n"/>
       <c r="D78" s="1285" t="n"/>
       <c r="E78" s="1285" t="n"/>
@@ -12032,16 +11520,8 @@
       <c r="H78" s="686" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="65" t="inlineStr">
-        <is>
-          <t>6.0.5</t>
-        </is>
-      </c>
-      <c r="B79" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Red contra incendio (gabinetes, red húmeda, siamesa)</t>
-        </is>
-      </c>
+      <c r="A79" s="65" t="n"/>
+      <c r="B79" s="43" t="n"/>
       <c r="C79" s="130" t="n"/>
       <c r="D79" s="1288" t="n"/>
       <c r="E79" s="1288" t="n"/>
@@ -12050,16 +11530,8 @@
       <c r="H79" s="684" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="64" t="inlineStr">
-        <is>
-          <t>6.0.6</t>
-        </is>
-      </c>
-      <c r="B80" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Instalación de aparatos sanitarios y grifería</t>
-        </is>
-      </c>
+      <c r="A80" s="64" t="n"/>
+      <c r="B80" s="42" t="n"/>
       <c r="C80" s="129" t="n"/>
       <c r="D80" s="1285" t="n"/>
       <c r="E80" s="1285" t="n"/>
@@ -12068,16 +11540,8 @@
       <c r="H80" s="686" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="65" t="inlineStr">
-        <is>
-          <t>6.0.7</t>
-        </is>
-      </c>
-      <c r="B81" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Instalaciones hidrosanitarias terminadas</t>
-        </is>
-      </c>
+      <c r="A81" s="65" t="n"/>
+      <c r="B81" s="43" t="n"/>
       <c r="C81" s="130" t="n"/>
       <c r="D81" s="1288" t="n"/>
       <c r="E81" s="1288" t="n"/>
@@ -12086,16 +11550,8 @@
       <c r="H81" s="684" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="1051">
-      <c r="A82" s="61" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B82" s="37" t="inlineStr">
-        <is>
-          <t>FASE 7 - INSTALACIONES ELÉCTRICAS Y ESPECIALES</t>
-        </is>
-      </c>
+      <c r="A82" s="61" t="n"/>
+      <c r="B82" s="37" t="n"/>
       <c r="C82" s="131" t="n"/>
       <c r="D82" s="1290" t="n"/>
       <c r="E82" s="1290" t="n"/>
@@ -12104,16 +11560,8 @@
       <c r="H82" s="692" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="65" t="inlineStr">
-        <is>
-          <t>7.0.1</t>
-        </is>
-      </c>
-      <c r="B83" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Acometida eléctrica y subestación / transformador</t>
-        </is>
-      </c>
+      <c r="A83" s="65" t="n"/>
+      <c r="B83" s="43" t="n"/>
       <c r="C83" s="130" t="n"/>
       <c r="D83" s="1288" t="n"/>
       <c r="E83" s="1288" t="n"/>
@@ -12122,16 +11570,8 @@
       <c r="H83" s="684" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="64" t="inlineStr">
-        <is>
-          <t>7.0.2</t>
-        </is>
-      </c>
-      <c r="B84" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Redes eléctricas internas (puntos, tuberías) - pisos 1 a 4</t>
-        </is>
-      </c>
+      <c r="A84" s="64" t="n"/>
+      <c r="B84" s="42" t="n"/>
       <c r="C84" s="129" t="n"/>
       <c r="D84" s="1285" t="n"/>
       <c r="E84" s="1285" t="n"/>
@@ -12140,16 +11580,8 @@
       <c r="H84" s="686" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="65" t="inlineStr">
-        <is>
-          <t>7.0.3</t>
-        </is>
-      </c>
-      <c r="B85" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Redes eléctricas internas (puntos, tuberías) - pisos 5 a 8</t>
-        </is>
-      </c>
+      <c r="A85" s="65" t="n"/>
+      <c r="B85" s="43" t="n"/>
       <c r="C85" s="130" t="n"/>
       <c r="D85" s="1288" t="n"/>
       <c r="E85" s="1288" t="n"/>
@@ -12158,16 +11590,8 @@
       <c r="H85" s="684" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="64" t="inlineStr">
-        <is>
-          <t>7.0.4</t>
-        </is>
-      </c>
-      <c r="B86" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Redes eléctricas internas (puntos, tuberías) - pisos 9 a 12</t>
-        </is>
-      </c>
+      <c r="A86" s="64" t="n"/>
+      <c r="B86" s="42" t="n"/>
       <c r="C86" s="129" t="n"/>
       <c r="D86" s="1285" t="n"/>
       <c r="E86" s="1285" t="n"/>
@@ -12176,16 +11600,8 @@
       <c r="H86" s="686" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="65" t="inlineStr">
-        <is>
-          <t>7.0.5</t>
-        </is>
-      </c>
-      <c r="B87" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tableros de distribución por piso y tablero general</t>
-        </is>
-      </c>
+      <c r="A87" s="65" t="n"/>
+      <c r="B87" s="43" t="n"/>
       <c r="C87" s="130" t="n"/>
       <c r="D87" s="1288" t="n"/>
       <c r="E87" s="1288" t="n"/>
@@ -12194,16 +11610,8 @@
       <c r="H87" s="684" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="64" t="inlineStr">
-        <is>
-          <t>7.0.6</t>
-        </is>
-      </c>
-      <c r="B88" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Sistema de puesta a tierra y pararrayos</t>
-        </is>
-      </c>
+      <c r="A88" s="64" t="n"/>
+      <c r="B88" s="42" t="n"/>
       <c r="C88" s="129" t="n"/>
       <c r="D88" s="1285" t="n"/>
       <c r="E88" s="1285" t="n"/>
@@ -12212,16 +11620,8 @@
       <c r="H88" s="686" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="65" t="inlineStr">
-        <is>
-          <t>7.0.7</t>
-        </is>
-      </c>
-      <c r="B89" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Planta eléctrica de emergencia</t>
-        </is>
-      </c>
+      <c r="A89" s="65" t="n"/>
+      <c r="B89" s="43" t="n"/>
       <c r="C89" s="130" t="n"/>
       <c r="D89" s="1288" t="n"/>
       <c r="E89" s="1288" t="n"/>
@@ -12230,16 +11630,8 @@
       <c r="H89" s="684" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="64" t="inlineStr">
-        <is>
-          <t>7.0.8</t>
-        </is>
-      </c>
-      <c r="B90" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Citofonía / portería eléctrica y control de acceso</t>
-        </is>
-      </c>
+      <c r="A90" s="64" t="n"/>
+      <c r="B90" s="42" t="n"/>
       <c r="C90" s="129" t="n"/>
       <c r="D90" s="1285" t="n"/>
       <c r="E90" s="1285" t="n"/>
@@ -12248,16 +11640,8 @@
       <c r="H90" s="686" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="65" t="inlineStr">
-        <is>
-          <t>7.0.9</t>
-        </is>
-      </c>
-      <c r="B91" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cableado estructurado (voz, datos, TV)</t>
-        </is>
-      </c>
+      <c r="A91" s="65" t="n"/>
+      <c r="B91" s="43" t="n"/>
       <c r="C91" s="130" t="n"/>
       <c r="D91" s="1288" t="n"/>
       <c r="E91" s="1288" t="n"/>
@@ -12266,16 +11650,8 @@
       <c r="H91" s="684" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="64" t="inlineStr">
-        <is>
-          <t>7.0.10</t>
-        </is>
-      </c>
-      <c r="B92" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Iluminación de zonas comunes y exteriores</t>
-        </is>
-      </c>
+      <c r="A92" s="64" t="n"/>
+      <c r="B92" s="42" t="n"/>
       <c r="C92" s="129" t="n"/>
       <c r="D92" s="1285" t="n"/>
       <c r="E92" s="1285" t="n"/>
@@ -12284,16 +11660,8 @@
       <c r="H92" s="686" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="65" t="inlineStr">
-        <is>
-          <t>7.0.11</t>
-        </is>
-      </c>
-      <c r="B93" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Instalaciones eléctricas terminadas</t>
-        </is>
-      </c>
+      <c r="A93" s="65" t="n"/>
+      <c r="B93" s="43" t="n"/>
       <c r="C93" s="130" t="n"/>
       <c r="D93" s="1288" t="n"/>
       <c r="E93" s="1288" t="n"/>
@@ -12302,16 +11670,8 @@
       <c r="H93" s="684" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="1051">
-      <c r="A94" s="61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B94" s="37" t="inlineStr">
-        <is>
-          <t>FASE 8 - INSTALACIÓN DE GAS NATURAL</t>
-        </is>
-      </c>
+      <c r="A94" s="61" t="n"/>
+      <c r="B94" s="37" t="n"/>
       <c r="C94" s="131" t="n"/>
       <c r="D94" s="1290" t="n"/>
       <c r="E94" s="1290" t="n"/>
@@ -12320,16 +11680,8 @@
       <c r="H94" s="692" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="65" t="inlineStr">
-        <is>
-          <t>8.0.1</t>
-        </is>
-      </c>
-      <c r="B95" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Acometida y sistema de medición centralizada de gas</t>
-        </is>
-      </c>
+      <c r="A95" s="65" t="n"/>
+      <c r="B95" s="43" t="n"/>
       <c r="C95" s="130" t="n"/>
       <c r="D95" s="1288" t="n"/>
       <c r="E95" s="1288" t="n"/>
@@ -12338,16 +11690,8 @@
       <c r="H95" s="684" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="64" t="inlineStr">
-        <is>
-          <t>8.0.2</t>
-        </is>
-      </c>
-      <c r="B96" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Red interna de gas natural - pisos 1 a 4</t>
-        </is>
-      </c>
+      <c r="A96" s="64" t="n"/>
+      <c r="B96" s="42" t="n"/>
       <c r="C96" s="129" t="n"/>
       <c r="D96" s="1285" t="n"/>
       <c r="E96" s="1285" t="n"/>
@@ -12356,16 +11700,8 @@
       <c r="H96" s="686" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="65" t="inlineStr">
-        <is>
-          <t>8.0.3</t>
-        </is>
-      </c>
-      <c r="B97" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Red interna de gas natural - pisos 5 a 8</t>
-        </is>
-      </c>
+      <c r="A97" s="65" t="n"/>
+      <c r="B97" s="43" t="n"/>
       <c r="C97" s="130" t="n"/>
       <c r="D97" s="1288" t="n"/>
       <c r="E97" s="1288" t="n"/>
@@ -12374,16 +11710,8 @@
       <c r="H97" s="684" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="64" t="inlineStr">
-        <is>
-          <t>8.0.4</t>
-        </is>
-      </c>
-      <c r="B98" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Red interna de gas natural - pisos 9 a 12</t>
-        </is>
-      </c>
+      <c r="A98" s="64" t="n"/>
+      <c r="B98" s="42" t="n"/>
       <c r="C98" s="129" t="n"/>
       <c r="D98" s="1285" t="n"/>
       <c r="E98" s="1285" t="n"/>
@@ -12392,16 +11720,8 @@
       <c r="H98" s="686" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="65" t="inlineStr">
-        <is>
-          <t>8.0.5</t>
-        </is>
-      </c>
-      <c r="B99" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Instalación de gas terminada</t>
-        </is>
-      </c>
+      <c r="A99" s="65" t="n"/>
+      <c r="B99" s="43" t="n"/>
       <c r="C99" s="130" t="n"/>
       <c r="D99" s="1288" t="n"/>
       <c r="E99" s="1288" t="n"/>
@@ -12410,16 +11730,8 @@
       <c r="H99" s="684" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="1051">
-      <c r="A100" s="61" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B100" s="37" t="inlineStr">
-        <is>
-          <t>FASE 9 - ASCENSORES</t>
-        </is>
-      </c>
+      <c r="A100" s="61" t="n"/>
+      <c r="B100" s="37" t="n"/>
       <c r="C100" s="131" t="n"/>
       <c r="D100" s="1290" t="n"/>
       <c r="E100" s="1290" t="n"/>
@@ -12428,16 +11740,8 @@
       <c r="H100" s="692" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="65" t="inlineStr">
-        <is>
-          <t>9.0.1</t>
-        </is>
-      </c>
-      <c r="B101" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Compra y fabricación de ascensores (long-lead)</t>
-        </is>
-      </c>
+      <c r="A101" s="65" t="n"/>
+      <c r="B101" s="43" t="n"/>
       <c r="C101" s="130" t="n"/>
       <c r="D101" s="1288" t="n"/>
       <c r="E101" s="1288" t="n"/>
@@ -12446,16 +11750,8 @@
       <c r="H101" s="684" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="64" t="inlineStr">
-        <is>
-          <t>9.0.2</t>
-        </is>
-      </c>
-      <c r="B102" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Foso y cuarto de máquinas (obra civil)</t>
-        </is>
-      </c>
+      <c r="A102" s="64" t="n"/>
+      <c r="B102" s="42" t="n"/>
       <c r="C102" s="129" t="n"/>
       <c r="D102" s="1285" t="n"/>
       <c r="E102" s="1285" t="n"/>
@@ -12464,16 +11760,8 @@
       <c r="H102" s="686" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="65" t="inlineStr">
-        <is>
-          <t>9.0.3</t>
-        </is>
-      </c>
-      <c r="B103" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Montaje de guías, cabina y equipos</t>
-        </is>
-      </c>
+      <c r="A103" s="65" t="n"/>
+      <c r="B103" s="43" t="n"/>
       <c r="C103" s="130" t="n"/>
       <c r="D103" s="1288" t="n"/>
       <c r="E103" s="1288" t="n"/>
@@ -12482,16 +11770,8 @@
       <c r="H103" s="684" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="64" t="inlineStr">
-        <is>
-          <t>9.0.4</t>
-        </is>
-      </c>
-      <c r="B104" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Pruebas, puesta en marcha y certificación</t>
-        </is>
-      </c>
+      <c r="A104" s="64" t="n"/>
+      <c r="B104" s="42" t="n"/>
       <c r="C104" s="129" t="n"/>
       <c r="D104" s="1285" t="n"/>
       <c r="E104" s="1285" t="n"/>
@@ -12500,16 +11780,8 @@
       <c r="H104" s="686" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="65" t="inlineStr">
-        <is>
-          <t>9.0.5</t>
-        </is>
-      </c>
-      <c r="B105" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Ascensores operativos y certificados</t>
-        </is>
-      </c>
+      <c r="A105" s="65" t="n"/>
+      <c r="B105" s="43" t="n"/>
       <c r="C105" s="130" t="n"/>
       <c r="D105" s="1288" t="n"/>
       <c r="E105" s="1288" t="n"/>
@@ -12518,16 +11790,8 @@
       <c r="H105" s="684" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="1051">
-      <c r="A106" s="61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B106" s="37" t="inlineStr">
-        <is>
-          <t>FASE 10 - CARPINTERÍA METÁLICA Y DE MADERA</t>
-        </is>
-      </c>
+      <c r="A106" s="61" t="n"/>
+      <c r="B106" s="37" t="n"/>
       <c r="C106" s="131" t="n"/>
       <c r="D106" s="1290" t="n"/>
       <c r="E106" s="1290" t="n"/>
@@ -12536,16 +11800,8 @@
       <c r="H106" s="692" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="65" t="inlineStr">
-        <is>
-          <t>10.0.1</t>
-        </is>
-      </c>
-      <c r="B107" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Ventanería en aluminio y vidrio (fachada)</t>
-        </is>
-      </c>
+      <c r="A107" s="65" t="n"/>
+      <c r="B107" s="43" t="n"/>
       <c r="C107" s="130" t="n"/>
       <c r="D107" s="1288" t="n"/>
       <c r="E107" s="1288" t="n"/>
@@ -12554,16 +11810,8 @@
       <c r="H107" s="684" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="64" t="inlineStr">
-        <is>
-          <t>10.0.2</t>
-        </is>
-      </c>
-      <c r="B108" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Baranda metálica de escaleras y balcones</t>
-        </is>
-      </c>
+      <c r="A108" s="64" t="n"/>
+      <c r="B108" s="42" t="n"/>
       <c r="C108" s="129" t="n"/>
       <c r="D108" s="1285" t="n"/>
       <c r="E108" s="1285" t="n"/>
@@ -12572,16 +11820,8 @@
       <c r="H108" s="686" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="65" t="inlineStr">
-        <is>
-          <t>10.0.3</t>
-        </is>
-      </c>
-      <c r="B109" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Puertas cortafuego en escaleras de emergencia</t>
-        </is>
-      </c>
+      <c r="A109" s="65" t="n"/>
+      <c r="B109" s="43" t="n"/>
       <c r="C109" s="130" t="n"/>
       <c r="D109" s="1288" t="n"/>
       <c r="E109" s="1288" t="n"/>
@@ -12590,16 +11830,8 @@
       <c r="H109" s="684" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="64" t="inlineStr">
-        <is>
-          <t>10.0.4</t>
-        </is>
-      </c>
-      <c r="B110" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Puertas de madera, puerta de acceso, closets y muebles de cocina</t>
-        </is>
-      </c>
+      <c r="A110" s="64" t="n"/>
+      <c r="B110" s="42" t="n"/>
       <c r="C110" s="129" t="n"/>
       <c r="D110" s="1285" t="n"/>
       <c r="E110" s="1285" t="n"/>
@@ -12608,16 +11840,8 @@
       <c r="H110" s="686" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="65" t="inlineStr">
-        <is>
-          <t>10.0.5</t>
-        </is>
-      </c>
-      <c r="B111" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Carpintería terminada</t>
-        </is>
-      </c>
+      <c r="A111" s="65" t="n"/>
+      <c r="B111" s="43" t="n"/>
       <c r="C111" s="130" t="n"/>
       <c r="D111" s="1288" t="n"/>
       <c r="E111" s="1288" t="n"/>
@@ -12626,16 +11850,8 @@
       <c r="H111" s="684" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="1051">
-      <c r="A112" s="61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B112" s="37" t="inlineStr">
-        <is>
-          <t>FASE 11 - ACABADOS</t>
-        </is>
-      </c>
+      <c r="A112" s="61" t="n"/>
+      <c r="B112" s="37" t="n"/>
       <c r="C112" s="131" t="n"/>
       <c r="D112" s="1290" t="n"/>
       <c r="E112" s="1290" t="n"/>
@@ -12644,16 +11860,8 @@
       <c r="H112" s="692" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="65" t="inlineStr">
-        <is>
-          <t>11.0.1</t>
-        </is>
-      </c>
-      <c r="B113" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Pisos, enchapes, cielo raso y pintura - pisos 1 a 4</t>
-        </is>
-      </c>
+      <c r="A113" s="65" t="n"/>
+      <c r="B113" s="43" t="n"/>
       <c r="C113" s="130" t="n"/>
       <c r="D113" s="1288" t="n"/>
       <c r="E113" s="1288" t="n"/>
@@ -12662,16 +11870,8 @@
       <c r="H113" s="684" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="64" t="inlineStr">
-        <is>
-          <t>11.0.2</t>
-        </is>
-      </c>
-      <c r="B114" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Pisos, enchapes, cielo raso y pintura - pisos 5 a 8</t>
-        </is>
-      </c>
+      <c r="A114" s="64" t="n"/>
+      <c r="B114" s="42" t="n"/>
       <c r="C114" s="129" t="n"/>
       <c r="D114" s="1285" t="n"/>
       <c r="E114" s="1285" t="n"/>
@@ -12680,16 +11880,8 @@
       <c r="H114" s="686" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="65" t="inlineStr">
-        <is>
-          <t>11.0.3</t>
-        </is>
-      </c>
-      <c r="B115" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Pisos, enchapes, cielo raso y pintura - pisos 9 a 12</t>
-        </is>
-      </c>
+      <c r="A115" s="65" t="n"/>
+      <c r="B115" s="43" t="n"/>
       <c r="C115" s="130" t="n"/>
       <c r="D115" s="1288" t="n"/>
       <c r="E115" s="1288" t="n"/>
@@ -12698,16 +11890,8 @@
       <c r="H115" s="684" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="64" t="inlineStr">
-        <is>
-          <t>11.0.4</t>
-        </is>
-      </c>
-      <c r="B116" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Piso en zonas comunes (granito/porcelanato alto tráfico)</t>
-        </is>
-      </c>
+      <c r="A116" s="64" t="n"/>
+      <c r="B116" s="42" t="n"/>
       <c r="C116" s="129" t="n"/>
       <c r="D116" s="1285" t="n"/>
       <c r="E116" s="1285" t="n"/>
@@ -12716,16 +11900,8 @@
       <c r="H116" s="686" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="65" t="inlineStr">
-        <is>
-          <t>11.0.5</t>
-        </is>
-      </c>
-      <c r="B117" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Estuco y pintura de fachada</t>
-        </is>
-      </c>
+      <c r="A117" s="65" t="n"/>
+      <c r="B117" s="43" t="n"/>
       <c r="C117" s="130" t="n"/>
       <c r="D117" s="1288" t="n"/>
       <c r="E117" s="1288" t="n"/>
@@ -12734,16 +11910,8 @@
       <c r="H117" s="684" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="64" t="inlineStr">
-        <is>
-          <t>11.0.6</t>
-        </is>
-      </c>
-      <c r="B118" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Acabados terminados</t>
-        </is>
-      </c>
+      <c r="A118" s="64" t="n"/>
+      <c r="B118" s="42" t="n"/>
       <c r="C118" s="129" t="n"/>
       <c r="D118" s="1285" t="n"/>
       <c r="E118" s="1285" t="n"/>
@@ -12752,16 +11920,8 @@
       <c r="H118" s="686" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="1051">
-      <c r="A119" s="61" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B119" s="37" t="inlineStr">
-        <is>
-          <t>FASE 12 - FACHADA</t>
-        </is>
-      </c>
+      <c r="A119" s="61" t="n"/>
+      <c r="B119" s="37" t="n"/>
       <c r="C119" s="131" t="n"/>
       <c r="D119" s="1290" t="n"/>
       <c r="E119" s="1290" t="n"/>
@@ -12770,16 +11930,8 @@
       <c r="H119" s="692" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="63" t="inlineStr">
-        <is>
-          <t>12.0.1</t>
-        </is>
-      </c>
-      <c r="B120" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Fachada en sistema de muro cortina / paneles arquitectónicos</t>
-        </is>
-      </c>
+      <c r="A120" s="63" t="n"/>
+      <c r="B120" s="41" t="n"/>
       <c r="C120" s="128" t="n"/>
       <c r="D120" s="1284" t="n"/>
       <c r="E120" s="1284" t="n"/>
@@ -12788,16 +11940,8 @@
       <c r="H120" s="691" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="65" t="inlineStr">
-        <is>
-          <t>12.0.2</t>
-        </is>
-      </c>
-      <c r="B121" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Aislamiento térmico y acústico de fachada</t>
-        </is>
-      </c>
+      <c r="A121" s="65" t="n"/>
+      <c r="B121" s="43" t="n"/>
       <c r="C121" s="130" t="n"/>
       <c r="D121" s="1288" t="n"/>
       <c r="E121" s="1288" t="n"/>
@@ -12806,16 +11950,8 @@
       <c r="H121" s="684" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="63" t="inlineStr">
-        <is>
-          <t>12.0.3</t>
-        </is>
-      </c>
-      <c r="B122" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Fachada terminada</t>
-        </is>
-      </c>
+      <c r="A122" s="63" t="n"/>
+      <c r="B122" s="41" t="n"/>
       <c r="C122" s="128" t="n"/>
       <c r="D122" s="1284" t="n"/>
       <c r="E122" s="1284" t="n"/>
@@ -12824,16 +11960,8 @@
       <c r="H122" s="691" t="n"/>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="1051">
-      <c r="A123" s="61" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B123" s="37" t="inlineStr">
-        <is>
-          <t>FASE 13 - URBANISMO Y OBRAS EXTERIORES</t>
-        </is>
-      </c>
+      <c r="A123" s="61" t="n"/>
+      <c r="B123" s="37" t="n"/>
       <c r="C123" s="131" t="n"/>
       <c r="D123" s="1290" t="n"/>
       <c r="E123" s="1290" t="n"/>
@@ -12842,16 +11970,8 @@
       <c r="H123" s="692" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="160" t="inlineStr">
-        <is>
-          <t>13.0.1</t>
-        </is>
-      </c>
-      <c r="B124" s="161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cerramiento definitivo, portería y control vehicular</t>
-        </is>
-      </c>
+      <c r="A124" s="160" t="n"/>
+      <c r="B124" s="161" t="n"/>
       <c r="C124" s="162" t="n"/>
       <c r="D124" s="1291" t="n"/>
       <c r="E124" s="1291" t="n"/>
@@ -12860,16 +11980,8 @@
       <c r="H124" s="691" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="163" t="inlineStr">
-        <is>
-          <t>13.0.2</t>
-        </is>
-      </c>
-      <c r="B125" s="164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Andenes, accesos peatonales y vehiculares</t>
-        </is>
-      </c>
+      <c r="A125" s="163" t="n"/>
+      <c r="B125" s="164" t="n"/>
       <c r="C125" s="165" t="n"/>
       <c r="D125" s="1292" t="n"/>
       <c r="E125" s="1292" t="n"/>
@@ -12881,16 +11993,8 @@
       <c r="K125" s="584" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="166" t="inlineStr">
-        <is>
-          <t>13.0.3</t>
-        </is>
-      </c>
-      <c r="B126" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Demarcación y señalización de parqueaderos</t>
-        </is>
-      </c>
+      <c r="A126" s="166" t="n"/>
+      <c r="B126" s="42" t="n"/>
       <c r="C126" s="129" t="n"/>
       <c r="D126" s="1285" t="n"/>
       <c r="E126" s="1285" t="n"/>
@@ -12900,16 +12004,8 @@
       <c r="K126" s="690" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="167" t="inlineStr">
-        <is>
-          <t>13.0.4</t>
-        </is>
-      </c>
-      <c r="B127" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Zonas verdes, paisajismo y riego</t>
-        </is>
-      </c>
+      <c r="A127" s="167" t="n"/>
+      <c r="B127" s="41" t="n"/>
       <c r="C127" s="128" t="n"/>
       <c r="D127" s="1284" t="n"/>
       <c r="E127" s="1284" t="n"/>
@@ -12919,16 +12015,8 @@
       <c r="K127" s="690" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="166" t="inlineStr">
-        <is>
-          <t>13.0.5</t>
-        </is>
-      </c>
-      <c r="B128" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Cuarto de basuras, shut de residuos y amoblamiento zonas comunes</t>
-        </is>
-      </c>
+      <c r="A128" s="166" t="n"/>
+      <c r="B128" s="42" t="n"/>
       <c r="C128" s="129" t="n"/>
       <c r="D128" s="1285" t="n"/>
       <c r="E128" s="1285" t="n"/>
@@ -12938,16 +12026,8 @@
       <c r="K128" s="690" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="167" t="inlineStr">
-        <is>
-          <t>13.0.6</t>
-        </is>
-      </c>
-      <c r="B129" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO: Obras exteriores y urbanismo terminadas</t>
-        </is>
-      </c>
+      <c r="A129" s="167" t="n"/>
+      <c r="B129" s="41" t="n"/>
       <c r="C129" s="128" t="n"/>
       <c r="D129" s="1284" t="n"/>
       <c r="E129" s="1284" t="n"/>
@@ -12957,16 +12037,8 @@
       <c r="K129" s="690" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="1051">
-      <c r="A130" s="168" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B130" s="37" t="inlineStr">
-        <is>
-          <t>FASE 14 - ASEO GENERAL, VARIOS Y ENTREGA</t>
-        </is>
-      </c>
+      <c r="A130" s="168" t="n"/>
+      <c r="B130" s="37" t="n"/>
       <c r="C130" s="131" t="n"/>
       <c r="D130" s="1290" t="n"/>
       <c r="E130" s="1290" t="n"/>
@@ -12976,16 +12048,8 @@
       <c r="K130" s="690" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="167" t="inlineStr">
-        <is>
-          <t>14.0.1</t>
-        </is>
-      </c>
-      <c r="B131" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Aseo general y limpieza fina de entrega</t>
-        </is>
-      </c>
+      <c r="A131" s="167" t="n"/>
+      <c r="B131" s="41" t="n"/>
       <c r="C131" s="128" t="n"/>
       <c r="D131" s="1284" t="n"/>
       <c r="E131" s="1284" t="n"/>
@@ -12995,16 +12059,8 @@
       <c r="K131" s="690" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="166" t="inlineStr">
-        <is>
-          <t>14.0.2</t>
-        </is>
-      </c>
-      <c r="B132" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Dotación contra incendios y señalización final</t>
-        </is>
-      </c>
+      <c r="A132" s="166" t="n"/>
+      <c r="B132" s="42" t="n"/>
       <c r="C132" s="129" t="n"/>
       <c r="D132" s="1285" t="n"/>
       <c r="E132" s="1285" t="n"/>
@@ -13014,16 +12070,8 @@
       <c r="K132" s="690" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="169" t="inlineStr">
-        <is>
-          <t>14.0.3</t>
-        </is>
-      </c>
-      <c r="B133" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Pólizas de estabilidad y seguros todo riesgo (trámite)</t>
-        </is>
-      </c>
+      <c r="A133" s="169" t="n"/>
+      <c r="B133" s="43" t="n"/>
       <c r="C133" s="130" t="n"/>
       <c r="D133" s="1288" t="n"/>
       <c r="E133" s="1288" t="n"/>
@@ -13033,16 +12081,8 @@
       <c r="K133" s="690" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="167" t="inlineStr">
-        <is>
-          <t>14.0.4</t>
-        </is>
-      </c>
-      <c r="B134" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Planos récord, manual de propiedad horizontal y actas de entrega</t>
-        </is>
-      </c>
+      <c r="A134" s="167" t="n"/>
+      <c r="B134" s="41" t="n"/>
       <c r="C134" s="128" t="n"/>
       <c r="D134" s="1284" t="n"/>
       <c r="E134" s="1284" t="n"/>
@@ -13052,16 +12092,8 @@
       <c r="K134" s="690" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="170" t="inlineStr">
-        <is>
-          <t>14.0.5</t>
-        </is>
-      </c>
-      <c r="B135" s="171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HITO FINAL: Entrega de la obra</t>
-        </is>
-      </c>
+      <c r="A135" s="170" t="n"/>
+      <c r="B135" s="171" t="n"/>
       <c r="C135" s="172" t="n"/>
       <c r="D135" s="1293" t="n"/>
       <c r="E135" s="1293" t="n"/>
@@ -13073,16 +12105,14 @@
       <c r="K135" s="606" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="233" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="K136" s="1140">
-        <f>J6</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A136" s="233" t="n"/>
+      <c r="K136" s="1140" t="n"/>
+    </row>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
     <row r="142">
       <c r="K142" s="159" t="n"/>
     </row>

--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -10876,8 +10876,16 @@
       <c r="K14" s="519" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="n"/>
-      <c r="B15" s="35" t="n"/>
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>EDIFICIO DE APARTAMENTOS 12 PISOS - BOGOTÁ D.C.</t>
+        </is>
+      </c>
       <c r="C15" s="36" t="n"/>
       <c r="D15" s="1281" t="n"/>
       <c r="E15" s="1281" t="n"/>
@@ -10887,8 +10895,16 @@
       <c r="K15" s="519" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="1051">
-      <c r="A16" s="156" t="n"/>
-      <c r="B16" s="157" t="n"/>
+      <c r="A16" s="156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="157" t="inlineStr">
+        <is>
+          <t>FASE 1 - PRELIMINARES, ESTUDIOS Y DISEÑOS</t>
+        </is>
+      </c>
       <c r="C16" s="158" t="n"/>
       <c r="D16" s="1282" t="n"/>
       <c r="E16" s="1282" t="n"/>
@@ -10900,8 +10916,16 @@
       <c r="K16" s="703" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="153" t="n"/>
-      <c r="B17" s="154" t="n"/>
+      <c r="A17" s="153" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B17" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Estudios y diseños</t>
+        </is>
+      </c>
       <c r="C17" s="155" t="n"/>
       <c r="D17" s="1283" t="n"/>
       <c r="E17" s="1283" t="n"/>
@@ -10910,8 +10934,16 @@
       <c r="H17" s="693" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="63" t="n"/>
-      <c r="B18" s="41" t="n"/>
+      <c r="A18" s="63" t="inlineStr">
+        <is>
+          <t>1.1.1</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estudio de suelos y geotecnia</t>
+        </is>
+      </c>
       <c r="C18" s="128" t="n"/>
       <c r="D18" s="1284" t="n"/>
       <c r="E18" s="1284" t="n"/>
@@ -10920,8 +10952,16 @@
       <c r="H18" s="691" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="63" t="n"/>
-      <c r="B19" s="41" t="n"/>
+      <c r="A19" s="63" t="inlineStr">
+        <is>
+          <t>1.1.2</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Diseño arquitectónico y estructural</t>
+        </is>
+      </c>
       <c r="C19" s="128" t="n"/>
       <c r="D19" s="1284" t="n"/>
       <c r="E19" s="1284" t="n"/>
@@ -10930,8 +10970,16 @@
       <c r="H19" s="691" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="64" t="n"/>
-      <c r="B20" s="42" t="n"/>
+      <c r="A20" s="64" t="inlineStr">
+        <is>
+          <t>1.1.3</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Diseño hidrosanitario, eléctrico y de gas</t>
+        </is>
+      </c>
       <c r="C20" s="129" t="n"/>
       <c r="D20" s="1285" t="n"/>
       <c r="E20" s="1285" t="n"/>
@@ -10940,8 +10988,16 @@
       <c r="H20" s="686" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="63" t="n"/>
-      <c r="B21" s="41" t="n"/>
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>1.1.4</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Trámite y expedición de licencia de construcción (curaduría)</t>
+        </is>
+      </c>
       <c r="C21" s="128" t="n"/>
       <c r="D21" s="1284" t="n"/>
       <c r="E21" s="1284" t="n"/>
@@ -10950,8 +11006,16 @@
       <c r="H21" s="691" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="n"/>
-      <c r="B22" s="39" t="n"/>
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Preliminares en el predio</t>
+        </is>
+      </c>
       <c r="C22" s="40" t="n"/>
       <c r="D22" s="1286" t="n"/>
       <c r="E22" s="1286" t="n"/>
@@ -10960,8 +11024,16 @@
       <c r="H22" s="693" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="63" t="n"/>
-      <c r="B23" s="41" t="n"/>
+      <c r="A23" s="63" t="inlineStr">
+        <is>
+          <t>1.2.1</t>
+        </is>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cerramiento provisional, campamento y oficina de obra</t>
+        </is>
+      </c>
       <c r="C23" s="128" t="n"/>
       <c r="D23" s="1284" t="n"/>
       <c r="E23" s="1284" t="n"/>
@@ -10970,8 +11042,16 @@
       <c r="H23" s="691" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="64" t="n"/>
-      <c r="B24" s="42" t="n"/>
+      <c r="A24" s="64" t="inlineStr">
+        <is>
+          <t>1.2.2</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Localización y replanteo topográfico general</t>
+        </is>
+      </c>
       <c r="C24" s="129" t="n"/>
       <c r="D24" s="1285" t="n"/>
       <c r="E24" s="1285" t="n"/>
@@ -10980,8 +11060,16 @@
       <c r="H24" s="686" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="63" t="n"/>
-      <c r="B25" s="41" t="n"/>
+      <c r="A25" s="63" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Descapote, demolición de estructuras existentes y limpieza</t>
+        </is>
+      </c>
       <c r="C25" s="128" t="n"/>
       <c r="D25" s="1284" t="n"/>
       <c r="E25" s="1284" t="n"/>
@@ -10990,8 +11078,16 @@
       <c r="H25" s="691" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="63" t="n"/>
-      <c r="B26" s="41" t="n"/>
+      <c r="A26" s="63" t="inlineStr">
+        <is>
+          <t>1.2.4</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Inicio de obra civil (fin de preliminares)</t>
+        </is>
+      </c>
       <c r="C26" s="128" t="n"/>
       <c r="D26" s="1284" t="n"/>
       <c r="E26" s="1284" t="n"/>
@@ -11000,8 +11096,16 @@
       <c r="H26" s="691" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="1051">
-      <c r="A27" s="61" t="n"/>
-      <c r="B27" s="37" t="n"/>
+      <c r="A27" s="61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>FASE 2 - EXCAVACIÓN Y CIMENTACIÓN</t>
+        </is>
+      </c>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="1287" t="n"/>
       <c r="E27" s="1287" t="n"/>
@@ -11010,8 +11114,16 @@
       <c r="H27" s="561" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="n"/>
-      <c r="B28" s="39" t="n"/>
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Excavación y contención</t>
+        </is>
+      </c>
       <c r="C28" s="40" t="n"/>
       <c r="D28" s="1286" t="n"/>
       <c r="E28" s="1286" t="n"/>
@@ -11020,8 +11132,16 @@
       <c r="H28" s="693" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="63" t="n"/>
-      <c r="B29" s="41" t="n"/>
+      <c r="A29" s="63" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Excavación mecánica de sótanos (2 niveles)</t>
+        </is>
+      </c>
       <c r="C29" s="128" t="n"/>
       <c r="D29" s="1284" t="n"/>
       <c r="E29" s="1284" t="n"/>
@@ -11030,8 +11150,16 @@
       <c r="H29" s="691" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="64" t="n"/>
-      <c r="B30" s="42" t="n"/>
+      <c r="A30" s="64" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cargue, transporte y disposición final de material sobrante</t>
+        </is>
+      </c>
       <c r="C30" s="129" t="n"/>
       <c r="D30" s="1285" t="n"/>
       <c r="E30" s="1285" t="n"/>
@@ -11040,8 +11168,16 @@
       <c r="H30" s="686" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="63" t="n"/>
-      <c r="B31" s="41" t="n"/>
+      <c r="A31" s="63" t="inlineStr">
+        <is>
+          <t>2.1.3</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Entibado y contención perimetral (pantalla anclada)</t>
+        </is>
+      </c>
       <c r="C31" s="128" t="n"/>
       <c r="D31" s="1284" t="n"/>
       <c r="E31" s="1284" t="n"/>
@@ -11050,8 +11186,16 @@
       <c r="H31" s="691" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="n"/>
-      <c r="B32" s="39" t="n"/>
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cimentación en concreto</t>
+        </is>
+      </c>
       <c r="C32" s="40" t="n"/>
       <c r="D32" s="1286" t="n"/>
       <c r="E32" s="1286" t="n"/>
@@ -11060,8 +11204,16 @@
       <c r="H32" s="693" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="n"/>
-      <c r="B33" s="41" t="n"/>
+      <c r="A33" s="63" t="inlineStr">
+        <is>
+          <t>2.2.1</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Solado o cimiento ciclópeo de limpieza</t>
+        </is>
+      </c>
       <c r="C33" s="128" t="n"/>
       <c r="D33" s="1284" t="n"/>
       <c r="E33" s="1284" t="n"/>
@@ -11070,8 +11222,16 @@
       <c r="H33" s="691" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="63" t="n"/>
-      <c r="B34" s="41" t="n"/>
+      <c r="A34" s="63" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Armado de acero de refuerzo - zapatas, dados y arranques de columna</t>
+        </is>
+      </c>
       <c r="C34" s="128" t="n"/>
       <c r="D34" s="1284" t="n"/>
       <c r="E34" s="1284" t="n"/>
@@ -11080,8 +11240,16 @@
       <c r="H34" s="691" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="63" t="n"/>
-      <c r="B35" s="41" t="n"/>
+      <c r="A35" s="63" t="inlineStr">
+        <is>
+          <t>2.2.3</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Fundida de zapatas y dados en concreto 3000 PSI</t>
+        </is>
+      </c>
       <c r="C35" s="128" t="n"/>
       <c r="D35" s="1284" t="n"/>
       <c r="E35" s="1284" t="n"/>
@@ -11090,8 +11258,16 @@
       <c r="H35" s="691" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="63" t="n"/>
-      <c r="B36" s="41" t="n"/>
+      <c r="A36" s="63" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Armado de acero de refuerzo - muros de contención</t>
+        </is>
+      </c>
       <c r="C36" s="128" t="n"/>
       <c r="D36" s="1284" t="n"/>
       <c r="E36" s="1284" t="n"/>
@@ -11100,8 +11276,16 @@
       <c r="H36" s="691" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="63" t="n"/>
-      <c r="B37" s="41" t="n"/>
+      <c r="A37" s="63" t="inlineStr">
+        <is>
+          <t>2.2.5</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Formaleta y fundida de muros de contención en concreto reforzado 3000 PSI</t>
+        </is>
+      </c>
       <c r="C37" s="128" t="n"/>
       <c r="D37" s="1284" t="n"/>
       <c r="E37" s="1284" t="n"/>
@@ -11110,8 +11294,16 @@
       <c r="H37" s="691" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="64" t="n"/>
-      <c r="B38" s="42" t="n"/>
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>2.2.6</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Vigas de cimentación (armado y fundida)</t>
+        </is>
+      </c>
       <c r="C38" s="129" t="n"/>
       <c r="D38" s="1285" t="n"/>
       <c r="E38" s="1285" t="n"/>
@@ -11120,8 +11312,16 @@
       <c r="H38" s="686" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="65" t="n"/>
-      <c r="B39" s="43" t="n"/>
+      <c r="A39" s="65" t="inlineStr">
+        <is>
+          <t>2.2.7</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Losa de cimentación / placa contrapiso sótano e=0.15m</t>
+        </is>
+      </c>
       <c r="C39" s="130" t="n"/>
       <c r="D39" s="1288" t="n"/>
       <c r="E39" s="1288" t="n"/>
@@ -11130,8 +11330,16 @@
       <c r="H39" s="684" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="63" t="n"/>
-      <c r="B40" s="41" t="n"/>
+      <c r="A40" s="63" t="inlineStr">
+        <is>
+          <t>2.2.8</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Impermeabilización de cimentación y muros de contención</t>
+        </is>
+      </c>
       <c r="C40" s="128" t="n"/>
       <c r="D40" s="1284" t="n"/>
       <c r="E40" s="1284" t="n"/>
@@ -11140,8 +11348,16 @@
       <c r="H40" s="691" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="63" t="n"/>
-      <c r="B41" s="41" t="n"/>
+      <c r="A41" s="63" t="inlineStr">
+        <is>
+          <t>2.2.9</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Cimentación terminada</t>
+        </is>
+      </c>
       <c r="C41" s="128" t="n"/>
       <c r="D41" s="1284" t="n"/>
       <c r="E41" s="1284" t="n"/>
@@ -11150,8 +11366,16 @@
       <c r="H41" s="691" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="1051">
-      <c r="A42" s="66" t="n"/>
-      <c r="B42" s="667" t="n"/>
+      <c r="A42" s="66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" s="667" t="inlineStr">
+        <is>
+          <t>FASE 3 - ESTRUCTURA EN CONCRETO (SUPERESTRUCTURA)</t>
+        </is>
+      </c>
       <c r="C42" s="44" t="n"/>
       <c r="D42" s="1289" t="n"/>
       <c r="E42" s="1289" t="n"/>
@@ -11160,8 +11384,16 @@
       <c r="H42" s="717" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="62" t="n"/>
-      <c r="B43" s="39" t="n"/>
+      <c r="A43" s="62" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Estructura de sótanos</t>
+        </is>
+      </c>
       <c r="C43" s="40" t="n"/>
       <c r="D43" s="1286" t="n"/>
       <c r="E43" s="1286" t="n"/>
@@ -11170,8 +11402,16 @@
       <c r="H43" s="693" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="63" t="n"/>
-      <c r="B44" s="41" t="n"/>
+      <c r="A44" s="63" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura sótano 1 (columnas, vigas, placa)</t>
+        </is>
+      </c>
       <c r="C44" s="128" t="n"/>
       <c r="D44" s="1284" t="n"/>
       <c r="E44" s="1284" t="n"/>
@@ -11180,8 +11420,16 @@
       <c r="H44" s="691" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="63" t="n"/>
-      <c r="B45" s="41" t="n"/>
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>3.1.2</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura sótano 2 (columnas, vigas, placa)</t>
+        </is>
+      </c>
       <c r="C45" s="128" t="n"/>
       <c r="D45" s="1284" t="n"/>
       <c r="E45" s="1284" t="n"/>
@@ -11190,8 +11438,16 @@
       <c r="H45" s="691" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="62" t="n"/>
-      <c r="B46" s="39" t="n"/>
+      <c r="A46" s="62" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Estructura de la torre (pisos 1 a 12)</t>
+        </is>
+      </c>
       <c r="C46" s="40" t="n"/>
       <c r="D46" s="1286" t="n"/>
       <c r="E46" s="1286" t="n"/>
@@ -11200,8 +11456,16 @@
       <c r="H46" s="693" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="63" t="n"/>
-      <c r="B47" s="41" t="n"/>
+      <c r="A47" s="63" t="inlineStr">
+        <is>
+          <t>3.2.1</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 1 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C47" s="128" t="n"/>
       <c r="D47" s="1284" t="n"/>
       <c r="E47" s="1284" t="n"/>
@@ -11210,8 +11474,16 @@
       <c r="H47" s="691" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="63" t="n"/>
-      <c r="B48" s="41" t="n"/>
+      <c r="A48" s="63" t="inlineStr">
+        <is>
+          <t>3.2.2</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 2 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C48" s="128" t="n"/>
       <c r="D48" s="1284" t="n"/>
       <c r="E48" s="1284" t="n"/>
@@ -11220,8 +11492,16 @@
       <c r="H48" s="691" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="63" t="n"/>
-      <c r="B49" s="41" t="n"/>
+      <c r="A49" s="63" t="inlineStr">
+        <is>
+          <t>3.2.3</t>
+        </is>
+      </c>
+      <c r="B49" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 3 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C49" s="128" t="n"/>
       <c r="D49" s="1284" t="n"/>
       <c r="E49" s="1284" t="n"/>
@@ -11230,8 +11510,16 @@
       <c r="H49" s="691" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="63" t="n"/>
-      <c r="B50" s="41" t="n"/>
+      <c r="A50" s="63" t="inlineStr">
+        <is>
+          <t>3.2.4</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 4 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C50" s="128" t="n"/>
       <c r="D50" s="1284" t="n"/>
       <c r="E50" s="1284" t="n"/>
@@ -11240,8 +11528,16 @@
       <c r="H50" s="691" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="63" t="n"/>
-      <c r="B51" s="41" t="n"/>
+      <c r="A51" s="63" t="inlineStr">
+        <is>
+          <t>3.2.5</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 5 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C51" s="128" t="n"/>
       <c r="D51" s="1284" t="n"/>
       <c r="E51" s="1284" t="n"/>
@@ -11250,8 +11546,16 @@
       <c r="H51" s="691" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="64" t="n"/>
-      <c r="B52" s="42" t="n"/>
+      <c r="A52" s="64" t="inlineStr">
+        <is>
+          <t>3.2.6</t>
+        </is>
+      </c>
+      <c r="B52" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 6 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C52" s="129" t="n"/>
       <c r="D52" s="1285" t="n"/>
       <c r="E52" s="1285" t="n"/>
@@ -11260,8 +11564,16 @@
       <c r="H52" s="686" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="65" t="n"/>
-      <c r="B53" s="43" t="n"/>
+      <c r="A53" s="65" t="inlineStr">
+        <is>
+          <t>3.2.7</t>
+        </is>
+      </c>
+      <c r="B53" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 7 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C53" s="130" t="n"/>
       <c r="D53" s="1288" t="n"/>
       <c r="E53" s="1288" t="n"/>
@@ -11270,8 +11582,16 @@
       <c r="H53" s="684" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="64" t="n"/>
-      <c r="B54" s="42" t="n"/>
+      <c r="A54" s="64" t="inlineStr">
+        <is>
+          <t>3.2.8</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 8 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C54" s="129" t="n"/>
       <c r="D54" s="1285" t="n"/>
       <c r="E54" s="1285" t="n"/>
@@ -11280,8 +11600,16 @@
       <c r="H54" s="686" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="65" t="n"/>
-      <c r="B55" s="43" t="n"/>
+      <c r="A55" s="65" t="inlineStr">
+        <is>
+          <t>3.2.9</t>
+        </is>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 9 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C55" s="130" t="n"/>
       <c r="D55" s="1288" t="n"/>
       <c r="E55" s="1288" t="n"/>
@@ -11290,8 +11618,16 @@
       <c r="H55" s="684" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="64" t="n"/>
-      <c r="B56" s="42" t="n"/>
+      <c r="A56" s="64" t="inlineStr">
+        <is>
+          <t>3.2.10</t>
+        </is>
+      </c>
+      <c r="B56" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 10 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C56" s="129" t="n"/>
       <c r="D56" s="1285" t="n"/>
       <c r="E56" s="1285" t="n"/>
@@ -11300,8 +11636,16 @@
       <c r="H56" s="686" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="65" t="n"/>
-      <c r="B57" s="43" t="n"/>
+      <c r="A57" s="65" t="inlineStr">
+        <is>
+          <t>3.2.11</t>
+        </is>
+      </c>
+      <c r="B57" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 11 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C57" s="130" t="n"/>
       <c r="D57" s="1288" t="n"/>
       <c r="E57" s="1288" t="n"/>
@@ -11310,8 +11654,16 @@
       <c r="H57" s="684" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="64" t="n"/>
-      <c r="B58" s="42" t="n"/>
+      <c r="A58" s="64" t="inlineStr">
+        <is>
+          <t>3.2.12</t>
+        </is>
+      </c>
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estructura piso 12 (columnas, vigas, placa de entrepiso)</t>
+        </is>
+      </c>
       <c r="C58" s="129" t="n"/>
       <c r="D58" s="1285" t="n"/>
       <c r="E58" s="1285" t="n"/>
@@ -11320,8 +11672,16 @@
       <c r="H58" s="686" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="62" t="n"/>
-      <c r="B59" s="39" t="n"/>
+      <c r="A59" s="62" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B59" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cubierta y remates estructurales</t>
+        </is>
+      </c>
       <c r="C59" s="40" t="n"/>
       <c r="D59" s="1286" t="n"/>
       <c r="E59" s="1286" t="n"/>
@@ -11330,8 +11690,16 @@
       <c r="H59" s="693" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="64" t="n"/>
-      <c r="B60" s="42" t="n"/>
+      <c r="A60" s="64" t="inlineStr">
+        <is>
+          <t>3.3.1</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Placa de cubierta y cuarto de máquinas</t>
+        </is>
+      </c>
       <c r="C60" s="129" t="n"/>
       <c r="D60" s="1285" t="n"/>
       <c r="E60" s="1285" t="n"/>
@@ -11340,8 +11708,16 @@
       <c r="H60" s="686" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="65" t="n"/>
-      <c r="B61" s="43" t="n"/>
+      <c r="A61" s="65" t="inlineStr">
+        <is>
+          <t>3.3.2</t>
+        </is>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Losa de tanque elevado</t>
+        </is>
+      </c>
       <c r="C61" s="130" t="n"/>
       <c r="D61" s="1288" t="n"/>
       <c r="E61" s="1288" t="n"/>
@@ -11350,8 +11726,16 @@
       <c r="H61" s="684" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="64" t="n"/>
-      <c r="B62" s="42" t="n"/>
+      <c r="A62" s="64" t="inlineStr">
+        <is>
+          <t>3.3.3</t>
+        </is>
+      </c>
+      <c r="B62" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Estructura de la torre terminada (topo de obra gris)</t>
+        </is>
+      </c>
       <c r="C62" s="129" t="n"/>
       <c r="D62" s="1285" t="n"/>
       <c r="E62" s="1285" t="n"/>
@@ -11360,8 +11744,16 @@
       <c r="H62" s="686" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="1051">
-      <c r="A63" s="61" t="n"/>
-      <c r="B63" s="37" t="n"/>
+      <c r="A63" s="61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B63" s="37" t="inlineStr">
+        <is>
+          <t>FASE 4 - MAMPOSTERÍA Y PAÑETES</t>
+        </is>
+      </c>
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="1290" t="n"/>
       <c r="E63" s="1290" t="n"/>
@@ -11370,8 +11762,16 @@
       <c r="H63" s="692" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="64" t="n"/>
-      <c r="B64" s="42" t="n"/>
+      <c r="A64" s="64" t="inlineStr">
+        <is>
+          <t>4.0.1</t>
+        </is>
+      </c>
+      <c r="B64" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Mampostería y pañetes - sótanos</t>
+        </is>
+      </c>
       <c r="C64" s="129" t="n"/>
       <c r="D64" s="1285" t="n"/>
       <c r="E64" s="1285" t="n"/>
@@ -11380,8 +11780,16 @@
       <c r="H64" s="686" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="63" t="n"/>
-      <c r="B65" s="41" t="n"/>
+      <c r="A65" s="63" t="inlineStr">
+        <is>
+          <t>4.0.2</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Mampostería y pañetes - pisos 1 a 4</t>
+        </is>
+      </c>
       <c r="C65" s="128" t="n"/>
       <c r="D65" s="1284" t="n"/>
       <c r="E65" s="1284" t="n"/>
@@ -11390,8 +11798,16 @@
       <c r="H65" s="691" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="63" t="n"/>
-      <c r="B66" s="41" t="n"/>
+      <c r="A66" s="63" t="inlineStr">
+        <is>
+          <t>4.0.3</t>
+        </is>
+      </c>
+      <c r="B66" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Mampostería y pañetes - pisos 5 a 8</t>
+        </is>
+      </c>
       <c r="C66" s="128" t="n"/>
       <c r="D66" s="1284" t="n"/>
       <c r="E66" s="1284" t="n"/>
@@ -11400,8 +11816,16 @@
       <c r="H66" s="691" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="63" t="n"/>
-      <c r="B67" s="41" t="n"/>
+      <c r="A67" s="63" t="inlineStr">
+        <is>
+          <t>4.0.4</t>
+        </is>
+      </c>
+      <c r="B67" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Mampostería y pañetes - pisos 9 a 12</t>
+        </is>
+      </c>
       <c r="C67" s="128" t="n"/>
       <c r="D67" s="1284" t="n"/>
       <c r="E67" s="1284" t="n"/>
@@ -11410,8 +11834,16 @@
       <c r="H67" s="691" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="63" t="n"/>
-      <c r="B68" s="41" t="n"/>
+      <c r="A68" s="63" t="inlineStr">
+        <is>
+          <t>4.0.5</t>
+        </is>
+      </c>
+      <c r="B68" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Mampostería y pañetes terminados</t>
+        </is>
+      </c>
       <c r="C68" s="128" t="n"/>
       <c r="D68" s="1284" t="n"/>
       <c r="E68" s="1284" t="n"/>
@@ -11420,8 +11852,16 @@
       <c r="H68" s="691" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="1051">
-      <c r="A69" s="61" t="n"/>
-      <c r="B69" s="37" t="n"/>
+      <c r="A69" s="61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B69" s="37" t="inlineStr">
+        <is>
+          <t>FASE 5 - CUBIERTA E IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
       <c r="C69" s="131" t="n"/>
       <c r="D69" s="1290" t="n"/>
       <c r="E69" s="1290" t="n"/>
@@ -11430,8 +11870,16 @@
       <c r="H69" s="692" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="64" t="n"/>
-      <c r="B70" s="42" t="n"/>
+      <c r="A70" s="64" t="inlineStr">
+        <is>
+          <t>5.0.1</t>
+        </is>
+      </c>
+      <c r="B70" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cubierta en teja termoacústica sobre estructura metálica</t>
+        </is>
+      </c>
       <c r="C70" s="129" t="n"/>
       <c r="D70" s="1285" t="n"/>
       <c r="E70" s="1285" t="n"/>
@@ -11440,8 +11888,16 @@
       <c r="H70" s="686" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="65" t="n"/>
-      <c r="B71" s="43" t="n"/>
+      <c r="A71" s="65" t="inlineStr">
+        <is>
+          <t>5.0.2</t>
+        </is>
+      </c>
+      <c r="B71" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Impermeabilización de cubiertas, terrazas y balcones</t>
+        </is>
+      </c>
       <c r="C71" s="130" t="n"/>
       <c r="D71" s="1288" t="n"/>
       <c r="E71" s="1288" t="n"/>
@@ -11450,8 +11906,16 @@
       <c r="H71" s="684" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="64" t="n"/>
-      <c r="B72" s="42" t="n"/>
+      <c r="A72" s="64" t="inlineStr">
+        <is>
+          <t>5.0.3</t>
+        </is>
+      </c>
+      <c r="B72" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Canales, bajantes de aguas lluvias y cuarto de máquinas/tanques</t>
+        </is>
+      </c>
       <c r="C72" s="129" t="n"/>
       <c r="D72" s="1285" t="n"/>
       <c r="E72" s="1285" t="n"/>
@@ -11460,8 +11924,16 @@
       <c r="H72" s="686" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="65" t="n"/>
-      <c r="B73" s="43" t="n"/>
+      <c r="A73" s="65" t="inlineStr">
+        <is>
+          <t>5.0.4</t>
+        </is>
+      </c>
+      <c r="B73" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Edificio bajo cubierta (dry-in)</t>
+        </is>
+      </c>
       <c r="C73" s="130" t="n"/>
       <c r="D73" s="1288" t="n"/>
       <c r="E73" s="1288" t="n"/>
@@ -11470,8 +11942,16 @@
       <c r="H73" s="684" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="1051">
-      <c r="A74" s="61" t="n"/>
-      <c r="B74" s="37" t="n"/>
+      <c r="A74" s="61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B74" s="37" t="inlineStr">
+        <is>
+          <t>FASE 6 - INSTALACIONES HIDROSANITARIAS</t>
+        </is>
+      </c>
       <c r="C74" s="131" t="n"/>
       <c r="D74" s="1290" t="n"/>
       <c r="E74" s="1290" t="n"/>
@@ -11480,8 +11960,16 @@
       <c r="H74" s="692" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="65" t="n"/>
-      <c r="B75" s="43" t="n"/>
+      <c r="A75" s="65" t="inlineStr">
+        <is>
+          <t>6.0.1</t>
+        </is>
+      </c>
+      <c r="B75" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Redes hidrosanitarias (punto agua/desagüe) - pisos 1 a 4</t>
+        </is>
+      </c>
       <c r="C75" s="130" t="n"/>
       <c r="D75" s="1288" t="n"/>
       <c r="E75" s="1288" t="n"/>
@@ -11490,8 +11978,16 @@
       <c r="H75" s="684" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="64" t="n"/>
-      <c r="B76" s="42" t="n"/>
+      <c r="A76" s="64" t="inlineStr">
+        <is>
+          <t>6.0.2</t>
+        </is>
+      </c>
+      <c r="B76" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Redes hidrosanitarias (punto agua/desagüe) - pisos 5 a 8</t>
+        </is>
+      </c>
       <c r="C76" s="129" t="n"/>
       <c r="D76" s="1285" t="n"/>
       <c r="E76" s="1285" t="n"/>
@@ -11500,8 +11996,16 @@
       <c r="H76" s="686" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="65" t="n"/>
-      <c r="B77" s="43" t="n"/>
+      <c r="A77" s="65" t="inlineStr">
+        <is>
+          <t>6.0.3</t>
+        </is>
+      </c>
+      <c r="B77" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Redes hidrosanitarias (punto agua/desagüe) - pisos 9 a 12</t>
+        </is>
+      </c>
       <c r="C77" s="130" t="n"/>
       <c r="D77" s="1288" t="n"/>
       <c r="E77" s="1288" t="n"/>
@@ -11510,8 +12014,16 @@
       <c r="H77" s="684" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="64" t="n"/>
-      <c r="B78" s="42" t="n"/>
+      <c r="A78" s="64" t="inlineStr">
+        <is>
+          <t>6.0.4</t>
+        </is>
+      </c>
+      <c r="B78" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cuarto de bombas, tanques de reserva y sistema hidroneumático</t>
+        </is>
+      </c>
       <c r="C78" s="129" t="n"/>
       <c r="D78" s="1285" t="n"/>
       <c r="E78" s="1285" t="n"/>
@@ -11520,8 +12032,16 @@
       <c r="H78" s="686" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="65" t="n"/>
-      <c r="B79" s="43" t="n"/>
+      <c r="A79" s="65" t="inlineStr">
+        <is>
+          <t>6.0.5</t>
+        </is>
+      </c>
+      <c r="B79" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Red contra incendio (gabinetes, red húmeda, siamesa)</t>
+        </is>
+      </c>
       <c r="C79" s="130" t="n"/>
       <c r="D79" s="1288" t="n"/>
       <c r="E79" s="1288" t="n"/>
@@ -11530,8 +12050,16 @@
       <c r="H79" s="684" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="64" t="n"/>
-      <c r="B80" s="42" t="n"/>
+      <c r="A80" s="64" t="inlineStr">
+        <is>
+          <t>6.0.6</t>
+        </is>
+      </c>
+      <c r="B80" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Instalación de aparatos sanitarios y grifería</t>
+        </is>
+      </c>
       <c r="C80" s="129" t="n"/>
       <c r="D80" s="1285" t="n"/>
       <c r="E80" s="1285" t="n"/>
@@ -11540,8 +12068,16 @@
       <c r="H80" s="686" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="65" t="n"/>
-      <c r="B81" s="43" t="n"/>
+      <c r="A81" s="65" t="inlineStr">
+        <is>
+          <t>6.0.7</t>
+        </is>
+      </c>
+      <c r="B81" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Instalaciones hidrosanitarias terminadas</t>
+        </is>
+      </c>
       <c r="C81" s="130" t="n"/>
       <c r="D81" s="1288" t="n"/>
       <c r="E81" s="1288" t="n"/>
@@ -11550,8 +12086,16 @@
       <c r="H81" s="684" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="1051">
-      <c r="A82" s="61" t="n"/>
-      <c r="B82" s="37" t="n"/>
+      <c r="A82" s="61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B82" s="37" t="inlineStr">
+        <is>
+          <t>FASE 7 - INSTALACIONES ELÉCTRICAS Y ESPECIALES</t>
+        </is>
+      </c>
       <c r="C82" s="131" t="n"/>
       <c r="D82" s="1290" t="n"/>
       <c r="E82" s="1290" t="n"/>
@@ -11560,8 +12104,16 @@
       <c r="H82" s="692" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="65" t="n"/>
-      <c r="B83" s="43" t="n"/>
+      <c r="A83" s="65" t="inlineStr">
+        <is>
+          <t>7.0.1</t>
+        </is>
+      </c>
+      <c r="B83" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Acometida eléctrica y subestación / transformador</t>
+        </is>
+      </c>
       <c r="C83" s="130" t="n"/>
       <c r="D83" s="1288" t="n"/>
       <c r="E83" s="1288" t="n"/>
@@ -11570,8 +12122,16 @@
       <c r="H83" s="684" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="64" t="n"/>
-      <c r="B84" s="42" t="n"/>
+      <c r="A84" s="64" t="inlineStr">
+        <is>
+          <t>7.0.2</t>
+        </is>
+      </c>
+      <c r="B84" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Redes eléctricas internas (puntos, tuberías) - pisos 1 a 4</t>
+        </is>
+      </c>
       <c r="C84" s="129" t="n"/>
       <c r="D84" s="1285" t="n"/>
       <c r="E84" s="1285" t="n"/>
@@ -11580,8 +12140,16 @@
       <c r="H84" s="686" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="65" t="n"/>
-      <c r="B85" s="43" t="n"/>
+      <c r="A85" s="65" t="inlineStr">
+        <is>
+          <t>7.0.3</t>
+        </is>
+      </c>
+      <c r="B85" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Redes eléctricas internas (puntos, tuberías) - pisos 5 a 8</t>
+        </is>
+      </c>
       <c r="C85" s="130" t="n"/>
       <c r="D85" s="1288" t="n"/>
       <c r="E85" s="1288" t="n"/>
@@ -11590,8 +12158,16 @@
       <c r="H85" s="684" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="64" t="n"/>
-      <c r="B86" s="42" t="n"/>
+      <c r="A86" s="64" t="inlineStr">
+        <is>
+          <t>7.0.4</t>
+        </is>
+      </c>
+      <c r="B86" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Redes eléctricas internas (puntos, tuberías) - pisos 9 a 12</t>
+        </is>
+      </c>
       <c r="C86" s="129" t="n"/>
       <c r="D86" s="1285" t="n"/>
       <c r="E86" s="1285" t="n"/>
@@ -11600,8 +12176,16 @@
       <c r="H86" s="686" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="65" t="n"/>
-      <c r="B87" s="43" t="n"/>
+      <c r="A87" s="65" t="inlineStr">
+        <is>
+          <t>7.0.5</t>
+        </is>
+      </c>
+      <c r="B87" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tableros de distribución por piso y tablero general</t>
+        </is>
+      </c>
       <c r="C87" s="130" t="n"/>
       <c r="D87" s="1288" t="n"/>
       <c r="E87" s="1288" t="n"/>
@@ -11610,8 +12194,16 @@
       <c r="H87" s="684" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="64" t="n"/>
-      <c r="B88" s="42" t="n"/>
+      <c r="A88" s="64" t="inlineStr">
+        <is>
+          <t>7.0.6</t>
+        </is>
+      </c>
+      <c r="B88" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Sistema de puesta a tierra y pararrayos</t>
+        </is>
+      </c>
       <c r="C88" s="129" t="n"/>
       <c r="D88" s="1285" t="n"/>
       <c r="E88" s="1285" t="n"/>
@@ -11620,8 +12212,16 @@
       <c r="H88" s="686" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="65" t="n"/>
-      <c r="B89" s="43" t="n"/>
+      <c r="A89" s="65" t="inlineStr">
+        <is>
+          <t>7.0.7</t>
+        </is>
+      </c>
+      <c r="B89" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Planta eléctrica de emergencia</t>
+        </is>
+      </c>
       <c r="C89" s="130" t="n"/>
       <c r="D89" s="1288" t="n"/>
       <c r="E89" s="1288" t="n"/>
@@ -11630,8 +12230,16 @@
       <c r="H89" s="684" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="64" t="n"/>
-      <c r="B90" s="42" t="n"/>
+      <c r="A90" s="64" t="inlineStr">
+        <is>
+          <t>7.0.8</t>
+        </is>
+      </c>
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Citofonía / portería eléctrica y control de acceso</t>
+        </is>
+      </c>
       <c r="C90" s="129" t="n"/>
       <c r="D90" s="1285" t="n"/>
       <c r="E90" s="1285" t="n"/>
@@ -11640,8 +12248,16 @@
       <c r="H90" s="686" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="65" t="n"/>
-      <c r="B91" s="43" t="n"/>
+      <c r="A91" s="65" t="inlineStr">
+        <is>
+          <t>7.0.9</t>
+        </is>
+      </c>
+      <c r="B91" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cableado estructurado (voz, datos, TV)</t>
+        </is>
+      </c>
       <c r="C91" s="130" t="n"/>
       <c r="D91" s="1288" t="n"/>
       <c r="E91" s="1288" t="n"/>
@@ -11650,8 +12266,16 @@
       <c r="H91" s="684" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="64" t="n"/>
-      <c r="B92" s="42" t="n"/>
+      <c r="A92" s="64" t="inlineStr">
+        <is>
+          <t>7.0.10</t>
+        </is>
+      </c>
+      <c r="B92" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Iluminación de zonas comunes y exteriores</t>
+        </is>
+      </c>
       <c r="C92" s="129" t="n"/>
       <c r="D92" s="1285" t="n"/>
       <c r="E92" s="1285" t="n"/>
@@ -11660,8 +12284,16 @@
       <c r="H92" s="686" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="65" t="n"/>
-      <c r="B93" s="43" t="n"/>
+      <c r="A93" s="65" t="inlineStr">
+        <is>
+          <t>7.0.11</t>
+        </is>
+      </c>
+      <c r="B93" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Instalaciones eléctricas terminadas</t>
+        </is>
+      </c>
       <c r="C93" s="130" t="n"/>
       <c r="D93" s="1288" t="n"/>
       <c r="E93" s="1288" t="n"/>
@@ -11670,8 +12302,16 @@
       <c r="H93" s="684" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="1051">
-      <c r="A94" s="61" t="n"/>
-      <c r="B94" s="37" t="n"/>
+      <c r="A94" s="61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B94" s="37" t="inlineStr">
+        <is>
+          <t>FASE 8 - INSTALACIÓN DE GAS NATURAL</t>
+        </is>
+      </c>
       <c r="C94" s="131" t="n"/>
       <c r="D94" s="1290" t="n"/>
       <c r="E94" s="1290" t="n"/>
@@ -11680,8 +12320,16 @@
       <c r="H94" s="692" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="65" t="n"/>
-      <c r="B95" s="43" t="n"/>
+      <c r="A95" s="65" t="inlineStr">
+        <is>
+          <t>8.0.1</t>
+        </is>
+      </c>
+      <c r="B95" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Acometida y sistema de medición centralizada de gas</t>
+        </is>
+      </c>
       <c r="C95" s="130" t="n"/>
       <c r="D95" s="1288" t="n"/>
       <c r="E95" s="1288" t="n"/>
@@ -11690,8 +12338,16 @@
       <c r="H95" s="684" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="64" t="n"/>
-      <c r="B96" s="42" t="n"/>
+      <c r="A96" s="64" t="inlineStr">
+        <is>
+          <t>8.0.2</t>
+        </is>
+      </c>
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Red interna de gas natural - pisos 1 a 4</t>
+        </is>
+      </c>
       <c r="C96" s="129" t="n"/>
       <c r="D96" s="1285" t="n"/>
       <c r="E96" s="1285" t="n"/>
@@ -11700,8 +12356,16 @@
       <c r="H96" s="686" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="65" t="n"/>
-      <c r="B97" s="43" t="n"/>
+      <c r="A97" s="65" t="inlineStr">
+        <is>
+          <t>8.0.3</t>
+        </is>
+      </c>
+      <c r="B97" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Red interna de gas natural - pisos 5 a 8</t>
+        </is>
+      </c>
       <c r="C97" s="130" t="n"/>
       <c r="D97" s="1288" t="n"/>
       <c r="E97" s="1288" t="n"/>
@@ -11710,8 +12374,16 @@
       <c r="H97" s="684" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="64" t="n"/>
-      <c r="B98" s="42" t="n"/>
+      <c r="A98" s="64" t="inlineStr">
+        <is>
+          <t>8.0.4</t>
+        </is>
+      </c>
+      <c r="B98" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Red interna de gas natural - pisos 9 a 12</t>
+        </is>
+      </c>
       <c r="C98" s="129" t="n"/>
       <c r="D98" s="1285" t="n"/>
       <c r="E98" s="1285" t="n"/>
@@ -11720,8 +12392,16 @@
       <c r="H98" s="686" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="65" t="n"/>
-      <c r="B99" s="43" t="n"/>
+      <c r="A99" s="65" t="inlineStr">
+        <is>
+          <t>8.0.5</t>
+        </is>
+      </c>
+      <c r="B99" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Instalación de gas terminada</t>
+        </is>
+      </c>
       <c r="C99" s="130" t="n"/>
       <c r="D99" s="1288" t="n"/>
       <c r="E99" s="1288" t="n"/>
@@ -11730,8 +12410,16 @@
       <c r="H99" s="684" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="1051">
-      <c r="A100" s="61" t="n"/>
-      <c r="B100" s="37" t="n"/>
+      <c r="A100" s="61" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B100" s="37" t="inlineStr">
+        <is>
+          <t>FASE 9 - ASCENSORES</t>
+        </is>
+      </c>
       <c r="C100" s="131" t="n"/>
       <c r="D100" s="1290" t="n"/>
       <c r="E100" s="1290" t="n"/>
@@ -11740,8 +12428,16 @@
       <c r="H100" s="692" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="65" t="n"/>
-      <c r="B101" s="43" t="n"/>
+      <c r="A101" s="65" t="inlineStr">
+        <is>
+          <t>9.0.1</t>
+        </is>
+      </c>
+      <c r="B101" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Compra y fabricación de ascensores (long-lead)</t>
+        </is>
+      </c>
       <c r="C101" s="130" t="n"/>
       <c r="D101" s="1288" t="n"/>
       <c r="E101" s="1288" t="n"/>
@@ -11750,8 +12446,16 @@
       <c r="H101" s="684" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="64" t="n"/>
-      <c r="B102" s="42" t="n"/>
+      <c r="A102" s="64" t="inlineStr">
+        <is>
+          <t>9.0.2</t>
+        </is>
+      </c>
+      <c r="B102" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Foso y cuarto de máquinas (obra civil)</t>
+        </is>
+      </c>
       <c r="C102" s="129" t="n"/>
       <c r="D102" s="1285" t="n"/>
       <c r="E102" s="1285" t="n"/>
@@ -11760,8 +12464,16 @@
       <c r="H102" s="686" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="65" t="n"/>
-      <c r="B103" s="43" t="n"/>
+      <c r="A103" s="65" t="inlineStr">
+        <is>
+          <t>9.0.3</t>
+        </is>
+      </c>
+      <c r="B103" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Montaje de guías, cabina y equipos</t>
+        </is>
+      </c>
       <c r="C103" s="130" t="n"/>
       <c r="D103" s="1288" t="n"/>
       <c r="E103" s="1288" t="n"/>
@@ -11770,8 +12482,16 @@
       <c r="H103" s="684" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="64" t="n"/>
-      <c r="B104" s="42" t="n"/>
+      <c r="A104" s="64" t="inlineStr">
+        <is>
+          <t>9.0.4</t>
+        </is>
+      </c>
+      <c r="B104" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Pruebas, puesta en marcha y certificación</t>
+        </is>
+      </c>
       <c r="C104" s="129" t="n"/>
       <c r="D104" s="1285" t="n"/>
       <c r="E104" s="1285" t="n"/>
@@ -11780,8 +12500,16 @@
       <c r="H104" s="686" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="65" t="n"/>
-      <c r="B105" s="43" t="n"/>
+      <c r="A105" s="65" t="inlineStr">
+        <is>
+          <t>9.0.5</t>
+        </is>
+      </c>
+      <c r="B105" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Ascensores operativos y certificados</t>
+        </is>
+      </c>
       <c r="C105" s="130" t="n"/>
       <c r="D105" s="1288" t="n"/>
       <c r="E105" s="1288" t="n"/>
@@ -11790,8 +12518,16 @@
       <c r="H105" s="684" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="1051">
-      <c r="A106" s="61" t="n"/>
-      <c r="B106" s="37" t="n"/>
+      <c r="A106" s="61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B106" s="37" t="inlineStr">
+        <is>
+          <t>FASE 10 - CARPINTERÍA METÁLICA Y DE MADERA</t>
+        </is>
+      </c>
       <c r="C106" s="131" t="n"/>
       <c r="D106" s="1290" t="n"/>
       <c r="E106" s="1290" t="n"/>
@@ -11800,8 +12536,16 @@
       <c r="H106" s="692" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="65" t="n"/>
-      <c r="B107" s="43" t="n"/>
+      <c r="A107" s="65" t="inlineStr">
+        <is>
+          <t>10.0.1</t>
+        </is>
+      </c>
+      <c r="B107" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Ventanería en aluminio y vidrio (fachada)</t>
+        </is>
+      </c>
       <c r="C107" s="130" t="n"/>
       <c r="D107" s="1288" t="n"/>
       <c r="E107" s="1288" t="n"/>
@@ -11810,8 +12554,16 @@
       <c r="H107" s="684" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="64" t="n"/>
-      <c r="B108" s="42" t="n"/>
+      <c r="A108" s="64" t="inlineStr">
+        <is>
+          <t>10.0.2</t>
+        </is>
+      </c>
+      <c r="B108" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Baranda metálica de escaleras y balcones</t>
+        </is>
+      </c>
       <c r="C108" s="129" t="n"/>
       <c r="D108" s="1285" t="n"/>
       <c r="E108" s="1285" t="n"/>
@@ -11820,8 +12572,16 @@
       <c r="H108" s="686" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="65" t="n"/>
-      <c r="B109" s="43" t="n"/>
+      <c r="A109" s="65" t="inlineStr">
+        <is>
+          <t>10.0.3</t>
+        </is>
+      </c>
+      <c r="B109" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Puertas cortafuego en escaleras de emergencia</t>
+        </is>
+      </c>
       <c r="C109" s="130" t="n"/>
       <c r="D109" s="1288" t="n"/>
       <c r="E109" s="1288" t="n"/>
@@ -11830,8 +12590,16 @@
       <c r="H109" s="684" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="64" t="n"/>
-      <c r="B110" s="42" t="n"/>
+      <c r="A110" s="64" t="inlineStr">
+        <is>
+          <t>10.0.4</t>
+        </is>
+      </c>
+      <c r="B110" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Puertas de madera, puerta de acceso, closets y muebles de cocina</t>
+        </is>
+      </c>
       <c r="C110" s="129" t="n"/>
       <c r="D110" s="1285" t="n"/>
       <c r="E110" s="1285" t="n"/>
@@ -11840,8 +12608,16 @@
       <c r="H110" s="686" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="65" t="n"/>
-      <c r="B111" s="43" t="n"/>
+      <c r="A111" s="65" t="inlineStr">
+        <is>
+          <t>10.0.5</t>
+        </is>
+      </c>
+      <c r="B111" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Carpintería terminada</t>
+        </is>
+      </c>
       <c r="C111" s="130" t="n"/>
       <c r="D111" s="1288" t="n"/>
       <c r="E111" s="1288" t="n"/>
@@ -11850,8 +12626,16 @@
       <c r="H111" s="684" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="1051">
-      <c r="A112" s="61" t="n"/>
-      <c r="B112" s="37" t="n"/>
+      <c r="A112" s="61" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B112" s="37" t="inlineStr">
+        <is>
+          <t>FASE 11 - ACABADOS</t>
+        </is>
+      </c>
       <c r="C112" s="131" t="n"/>
       <c r="D112" s="1290" t="n"/>
       <c r="E112" s="1290" t="n"/>
@@ -11860,8 +12644,16 @@
       <c r="H112" s="692" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="65" t="n"/>
-      <c r="B113" s="43" t="n"/>
+      <c r="A113" s="65" t="inlineStr">
+        <is>
+          <t>11.0.1</t>
+        </is>
+      </c>
+      <c r="B113" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Pisos, enchapes, cielo raso y pintura - pisos 1 a 4</t>
+        </is>
+      </c>
       <c r="C113" s="130" t="n"/>
       <c r="D113" s="1288" t="n"/>
       <c r="E113" s="1288" t="n"/>
@@ -11870,8 +12662,16 @@
       <c r="H113" s="684" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="64" t="n"/>
-      <c r="B114" s="42" t="n"/>
+      <c r="A114" s="64" t="inlineStr">
+        <is>
+          <t>11.0.2</t>
+        </is>
+      </c>
+      <c r="B114" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Pisos, enchapes, cielo raso y pintura - pisos 5 a 8</t>
+        </is>
+      </c>
       <c r="C114" s="129" t="n"/>
       <c r="D114" s="1285" t="n"/>
       <c r="E114" s="1285" t="n"/>
@@ -11880,8 +12680,16 @@
       <c r="H114" s="686" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="65" t="n"/>
-      <c r="B115" s="43" t="n"/>
+      <c r="A115" s="65" t="inlineStr">
+        <is>
+          <t>11.0.3</t>
+        </is>
+      </c>
+      <c r="B115" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Pisos, enchapes, cielo raso y pintura - pisos 9 a 12</t>
+        </is>
+      </c>
       <c r="C115" s="130" t="n"/>
       <c r="D115" s="1288" t="n"/>
       <c r="E115" s="1288" t="n"/>
@@ -11890,8 +12698,16 @@
       <c r="H115" s="684" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="64" t="n"/>
-      <c r="B116" s="42" t="n"/>
+      <c r="A116" s="64" t="inlineStr">
+        <is>
+          <t>11.0.4</t>
+        </is>
+      </c>
+      <c r="B116" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Piso en zonas comunes (granito/porcelanato alto tráfico)</t>
+        </is>
+      </c>
       <c r="C116" s="129" t="n"/>
       <c r="D116" s="1285" t="n"/>
       <c r="E116" s="1285" t="n"/>
@@ -11900,8 +12716,16 @@
       <c r="H116" s="686" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="65" t="n"/>
-      <c r="B117" s="43" t="n"/>
+      <c r="A117" s="65" t="inlineStr">
+        <is>
+          <t>11.0.5</t>
+        </is>
+      </c>
+      <c r="B117" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Estuco y pintura de fachada</t>
+        </is>
+      </c>
       <c r="C117" s="130" t="n"/>
       <c r="D117" s="1288" t="n"/>
       <c r="E117" s="1288" t="n"/>
@@ -11910,8 +12734,16 @@
       <c r="H117" s="684" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="64" t="n"/>
-      <c r="B118" s="42" t="n"/>
+      <c r="A118" s="64" t="inlineStr">
+        <is>
+          <t>11.0.6</t>
+        </is>
+      </c>
+      <c r="B118" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Acabados terminados</t>
+        </is>
+      </c>
       <c r="C118" s="129" t="n"/>
       <c r="D118" s="1285" t="n"/>
       <c r="E118" s="1285" t="n"/>
@@ -11920,8 +12752,16 @@
       <c r="H118" s="686" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="1051">
-      <c r="A119" s="61" t="n"/>
-      <c r="B119" s="37" t="n"/>
+      <c r="A119" s="61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B119" s="37" t="inlineStr">
+        <is>
+          <t>FASE 12 - FACHADA</t>
+        </is>
+      </c>
       <c r="C119" s="131" t="n"/>
       <c r="D119" s="1290" t="n"/>
       <c r="E119" s="1290" t="n"/>
@@ -11930,8 +12770,16 @@
       <c r="H119" s="692" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="63" t="n"/>
-      <c r="B120" s="41" t="n"/>
+      <c r="A120" s="63" t="inlineStr">
+        <is>
+          <t>12.0.1</t>
+        </is>
+      </c>
+      <c r="B120" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Fachada en sistema de muro cortina / paneles arquitectónicos</t>
+        </is>
+      </c>
       <c r="C120" s="128" t="n"/>
       <c r="D120" s="1284" t="n"/>
       <c r="E120" s="1284" t="n"/>
@@ -11940,8 +12788,16 @@
       <c r="H120" s="691" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="65" t="n"/>
-      <c r="B121" s="43" t="n"/>
+      <c r="A121" s="65" t="inlineStr">
+        <is>
+          <t>12.0.2</t>
+        </is>
+      </c>
+      <c r="B121" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Aislamiento térmico y acústico de fachada</t>
+        </is>
+      </c>
       <c r="C121" s="130" t="n"/>
       <c r="D121" s="1288" t="n"/>
       <c r="E121" s="1288" t="n"/>
@@ -11950,8 +12806,16 @@
       <c r="H121" s="684" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="63" t="n"/>
-      <c r="B122" s="41" t="n"/>
+      <c r="A122" s="63" t="inlineStr">
+        <is>
+          <t>12.0.3</t>
+        </is>
+      </c>
+      <c r="B122" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Fachada terminada</t>
+        </is>
+      </c>
       <c r="C122" s="128" t="n"/>
       <c r="D122" s="1284" t="n"/>
       <c r="E122" s="1284" t="n"/>
@@ -11960,8 +12824,16 @@
       <c r="H122" s="691" t="n"/>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="1051">
-      <c r="A123" s="61" t="n"/>
-      <c r="B123" s="37" t="n"/>
+      <c r="A123" s="61" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B123" s="37" t="inlineStr">
+        <is>
+          <t>FASE 13 - URBANISMO Y OBRAS EXTERIORES</t>
+        </is>
+      </c>
       <c r="C123" s="131" t="n"/>
       <c r="D123" s="1290" t="n"/>
       <c r="E123" s="1290" t="n"/>
@@ -11970,8 +12842,16 @@
       <c r="H123" s="692" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="160" t="n"/>
-      <c r="B124" s="161" t="n"/>
+      <c r="A124" s="160" t="inlineStr">
+        <is>
+          <t>13.0.1</t>
+        </is>
+      </c>
+      <c r="B124" s="161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cerramiento definitivo, portería y control vehicular</t>
+        </is>
+      </c>
       <c r="C124" s="162" t="n"/>
       <c r="D124" s="1291" t="n"/>
       <c r="E124" s="1291" t="n"/>
@@ -11980,8 +12860,16 @@
       <c r="H124" s="691" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="163" t="n"/>
-      <c r="B125" s="164" t="n"/>
+      <c r="A125" s="163" t="inlineStr">
+        <is>
+          <t>13.0.2</t>
+        </is>
+      </c>
+      <c r="B125" s="164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Andenes, accesos peatonales y vehiculares</t>
+        </is>
+      </c>
       <c r="C125" s="165" t="n"/>
       <c r="D125" s="1292" t="n"/>
       <c r="E125" s="1292" t="n"/>
@@ -11993,8 +12881,16 @@
       <c r="K125" s="584" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="166" t="n"/>
-      <c r="B126" s="42" t="n"/>
+      <c r="A126" s="166" t="inlineStr">
+        <is>
+          <t>13.0.3</t>
+        </is>
+      </c>
+      <c r="B126" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Demarcación y señalización de parqueaderos</t>
+        </is>
+      </c>
       <c r="C126" s="129" t="n"/>
       <c r="D126" s="1285" t="n"/>
       <c r="E126" s="1285" t="n"/>
@@ -12004,8 +12900,16 @@
       <c r="K126" s="690" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="167" t="n"/>
-      <c r="B127" s="41" t="n"/>
+      <c r="A127" s="167" t="inlineStr">
+        <is>
+          <t>13.0.4</t>
+        </is>
+      </c>
+      <c r="B127" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Zonas verdes, paisajismo y riego</t>
+        </is>
+      </c>
       <c r="C127" s="128" t="n"/>
       <c r="D127" s="1284" t="n"/>
       <c r="E127" s="1284" t="n"/>
@@ -12015,8 +12919,16 @@
       <c r="K127" s="690" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="166" t="n"/>
-      <c r="B128" s="42" t="n"/>
+      <c r="A128" s="166" t="inlineStr">
+        <is>
+          <t>13.0.5</t>
+        </is>
+      </c>
+      <c r="B128" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Cuarto de basuras, shut de residuos y amoblamiento zonas comunes</t>
+        </is>
+      </c>
       <c r="C128" s="129" t="n"/>
       <c r="D128" s="1285" t="n"/>
       <c r="E128" s="1285" t="n"/>
@@ -12026,8 +12938,16 @@
       <c r="K128" s="690" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="167" t="n"/>
-      <c r="B129" s="41" t="n"/>
+      <c r="A129" s="167" t="inlineStr">
+        <is>
+          <t>13.0.6</t>
+        </is>
+      </c>
+      <c r="B129" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO: Obras exteriores y urbanismo terminadas</t>
+        </is>
+      </c>
       <c r="C129" s="128" t="n"/>
       <c r="D129" s="1284" t="n"/>
       <c r="E129" s="1284" t="n"/>
@@ -12037,8 +12957,16 @@
       <c r="K129" s="690" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="1051">
-      <c r="A130" s="168" t="n"/>
-      <c r="B130" s="37" t="n"/>
+      <c r="A130" s="168" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B130" s="37" t="inlineStr">
+        <is>
+          <t>FASE 14 - ASEO GENERAL, VARIOS Y ENTREGA</t>
+        </is>
+      </c>
       <c r="C130" s="131" t="n"/>
       <c r="D130" s="1290" t="n"/>
       <c r="E130" s="1290" t="n"/>
@@ -12048,8 +12976,16 @@
       <c r="K130" s="690" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="167" t="n"/>
-      <c r="B131" s="41" t="n"/>
+      <c r="A131" s="167" t="inlineStr">
+        <is>
+          <t>14.0.1</t>
+        </is>
+      </c>
+      <c r="B131" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Aseo general y limpieza fina de entrega</t>
+        </is>
+      </c>
       <c r="C131" s="128" t="n"/>
       <c r="D131" s="1284" t="n"/>
       <c r="E131" s="1284" t="n"/>
@@ -12059,8 +12995,16 @@
       <c r="K131" s="690" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="166" t="n"/>
-      <c r="B132" s="42" t="n"/>
+      <c r="A132" s="166" t="inlineStr">
+        <is>
+          <t>14.0.2</t>
+        </is>
+      </c>
+      <c r="B132" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Dotación contra incendios y señalización final</t>
+        </is>
+      </c>
       <c r="C132" s="129" t="n"/>
       <c r="D132" s="1285" t="n"/>
       <c r="E132" s="1285" t="n"/>
@@ -12070,8 +13014,16 @@
       <c r="K132" s="690" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="169" t="n"/>
-      <c r="B133" s="43" t="n"/>
+      <c r="A133" s="169" t="inlineStr">
+        <is>
+          <t>14.0.3</t>
+        </is>
+      </c>
+      <c r="B133" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Pólizas de estabilidad y seguros todo riesgo (trámite)</t>
+        </is>
+      </c>
       <c r="C133" s="130" t="n"/>
       <c r="D133" s="1288" t="n"/>
       <c r="E133" s="1288" t="n"/>
@@ -12081,8 +13033,16 @@
       <c r="K133" s="690" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="167" t="n"/>
-      <c r="B134" s="41" t="n"/>
+      <c r="A134" s="167" t="inlineStr">
+        <is>
+          <t>14.0.4</t>
+        </is>
+      </c>
+      <c r="B134" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Planos récord, manual de propiedad horizontal y actas de entrega</t>
+        </is>
+      </c>
       <c r="C134" s="128" t="n"/>
       <c r="D134" s="1284" t="n"/>
       <c r="E134" s="1284" t="n"/>
@@ -12092,8 +13052,16 @@
       <c r="K134" s="690" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="170" t="n"/>
-      <c r="B135" s="171" t="n"/>
+      <c r="A135" s="170" t="inlineStr">
+        <is>
+          <t>14.0.5</t>
+        </is>
+      </c>
+      <c r="B135" s="171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HITO FINAL: Entrega de la obra</t>
+        </is>
+      </c>
       <c r="C135" s="172" t="n"/>
       <c r="D135" s="1293" t="n"/>
       <c r="E135" s="1293" t="n"/>
@@ -12105,14 +13073,16 @@
       <c r="K135" s="606" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="233" t="n"/>
-      <c r="K136" s="1140" t="n"/>
-    </row>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
+      <c r="A136" s="233" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="K136" s="1140">
+        <f>J6</f>
+        <v/>
+      </c>
+    </row>
     <row r="142">
       <c r="K142" s="159" t="n"/>
     </row>

--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -9945,464 +9945,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1228,6 +1228,11 @@
       <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="76">
@@ -6573,7 +6578,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9798,6 +9803,9 @@
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10019,7 +10027,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10215,7 +10223,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10306,7 +10314,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10339,7 +10347,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>

--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1233,6 +1233,10 @@
       <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="76">
@@ -6578,7 +6582,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1308">
+  <cellXfs count="1309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9807,6 +9811,7 @@
     <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -23,6 +23,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="170">
     <font>
@@ -1688,7 +1689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6573,6 +6574,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6582,7 +6597,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1309">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9812,6 +9827,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10627,7 +10654,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K142"/>

--- a/public/plantilla-cronograma.xlsx
+++ b/public/plantilla-cronograma.xlsx
@@ -10403,31 +10403,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
